--- a/output/spreadsheet/pyg_inc_2026.xlsx
+++ b/output/spreadsheet/pyg_inc_2026.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="165" formatCode="0.00000000"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);-"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,10 +52,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
     </font>
     <font>
       <b val="1"/>
@@ -128,9 +124,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -146,17 +142,16 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -532,7 +527,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -703,23 +698,59 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Actualizado: 03/04/2026 08:03 h</t>
+          <t>Actualizado: 04/04/2026 12:00 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
+      <c r="D3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),0)&lt;TODAY(),D5/DAY(EOMONTH(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),0)),D5/MAX(NOW()-DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="E3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),0)&lt;TODAY(),E5/DAY(EOMONTH(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),0)),E5/MAX(NOW()-DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),0)&lt;TODAY(),F5/DAY(EOMONTH(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),0)),F5/MAX(NOW()-DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),0)&lt;TODAY(),G5/DAY(EOMONTH(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),0)),G5/MAX(NOW()-DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),0)&lt;TODAY(),H5/DAY(EOMONTH(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),0)),H5/MAX(NOW()-DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),0)&lt;TODAY(),I5/DAY(EOMONTH(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),0)),I5/MAX(NOW()-DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),0)&lt;TODAY(),J5/DAY(EOMONTH(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),0)),J5/MAX(NOW()-DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),0)&lt;TODAY(),K5/DAY(EOMONTH(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),0)),K5/MAX(NOW()-DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="L3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),0)&lt;TODAY(),L5/DAY(EOMONTH(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),0)),L5/MAX(NOW()-DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),0)&lt;TODAY(),M5/DAY(EOMONTH(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),0)),M5/MAX(NOW()-DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="N3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),0)&lt;TODAY(),N5/DAY(EOMONTH(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),0)),N5/MAX(NOW()-DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),0)&lt;TODAY(),O5/DAY(EOMONTH(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),0)),O5/MAX(NOW()-DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
     </row>
@@ -732,51 +763,51 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6">
-        <f>D5+D8</f>
+        <f>D5+D8+D9</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>E5+E8</f>
+        <f>E5+E8+E9</f>
         <v/>
       </c>
       <c r="F4" s="6">
-        <f>F5+F8</f>
+        <f>F5+F8+F9</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>G5+G8</f>
+        <f>G5+G8+G9</f>
         <v/>
       </c>
       <c r="H4" s="6">
-        <f>H5+H8</f>
+        <f>H5+H8+H9</f>
         <v/>
       </c>
       <c r="I4" s="6">
-        <f>I5+I8</f>
+        <f>I5+I8+I9</f>
         <v/>
       </c>
       <c r="J4" s="6">
-        <f>J5+J8</f>
+        <f>J5+J8+J9</f>
         <v/>
       </c>
       <c r="K4" s="6">
-        <f>K5+K8</f>
+        <f>K5+K8+K9</f>
         <v/>
       </c>
       <c r="L4" s="6">
-        <f>L5+L8</f>
+        <f>L5+L8+L9</f>
         <v/>
       </c>
       <c r="M4" s="6">
-        <f>M5+M8</f>
+        <f>M5+M8+M9</f>
         <v/>
       </c>
       <c r="N4" s="6">
-        <f>N5+N8</f>
+        <f>N5+N8+N9</f>
         <v/>
       </c>
       <c r="O4" s="6">
-        <f>O5+O8</f>
+        <f>O5+O8+O9</f>
         <v/>
       </c>
       <c r="P4" s="6">
@@ -979,304 +1010,300 @@
         </is>
       </c>
     </row>
-    <row r="8" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Otros ingresos</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="10" t="n"/>
-      <c r="J8" s="10" t="n"/>
-      <c r="K8" s="10" t="n"/>
-      <c r="L8" s="10" t="n"/>
-      <c r="M8" s="10" t="n"/>
-      <c r="N8" s="10" t="n"/>
-      <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10">
+    <row r="8" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Services</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P8" s="8">
         <f>SUM(D8:O8)</f>
         <v/>
       </c>
-      <c r="Q8" s="10" t="n"/>
-    </row>
-    <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4">
+      <c r="Q8" s="8" t="n"/>
+    </row>
+    <row r="9" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Uncategorized income</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10">
         <f>SUM(D9:O9)</f>
         <v/>
       </c>
-      <c r="Q9" s="4" t="n"/>
+      <c r="Q9" s="10" t="n"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4">
+        <f>SUM(D10:O10)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="12" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6">
-        <f>D11+D30</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>E11+E30</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>F11+F30</f>
-        <v/>
-      </c>
-      <c r="G10" s="6">
-        <f>G11+G30</f>
-        <v/>
-      </c>
-      <c r="H10" s="6">
-        <f>H11+H30</f>
-        <v/>
-      </c>
-      <c r="I10" s="6">
-        <f>I11+I30</f>
-        <v/>
-      </c>
-      <c r="J10" s="6">
-        <f>J11+J30</f>
-        <v/>
-      </c>
-      <c r="K10" s="6">
-        <f>K11+K30</f>
-        <v/>
-      </c>
-      <c r="L10" s="6">
-        <f>L11+L30</f>
-        <v/>
-      </c>
-      <c r="M10" s="6">
-        <f>M11+M30</f>
-        <v/>
-      </c>
-      <c r="N10" s="6">
-        <f>N11+N30</f>
-        <v/>
-      </c>
-      <c r="O10" s="6">
-        <f>O11+O30</f>
-        <v/>
-      </c>
-      <c r="P10" s="6">
-        <f>SUM(D10:O10)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n"/>
-    </row>
-    <row r="11" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6">
+        <f>D12+D31</f>
+        <v/>
+      </c>
+      <c r="E11" s="6">
+        <f>E12+E31</f>
+        <v/>
+      </c>
+      <c r="F11" s="6">
+        <f>F12+F31</f>
+        <v/>
+      </c>
+      <c r="G11" s="6">
+        <f>G12+G31</f>
+        <v/>
+      </c>
+      <c r="H11" s="6">
+        <f>H12+H31</f>
+        <v/>
+      </c>
+      <c r="I11" s="6">
+        <f>I12+I31</f>
+        <v/>
+      </c>
+      <c r="J11" s="6">
+        <f>J12+J31</f>
+        <v/>
+      </c>
+      <c r="K11" s="6">
+        <f>K12+K31</f>
+        <v/>
+      </c>
+      <c r="L11" s="6">
+        <f>L12+L31</f>
+        <v/>
+      </c>
+      <c r="M11" s="6">
+        <f>M12+M31</f>
+        <v/>
+      </c>
+      <c r="N11" s="6">
+        <f>N12+N31</f>
+        <v/>
+      </c>
+      <c r="O11" s="6">
+        <f>O12+O31</f>
+        <v/>
+      </c>
+      <c r="P11" s="6">
+        <f>SUM(D11:O11)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n"/>
+    </row>
+    <row r="12" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  COGS</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8">
-        <f>D12+D17+D20</f>
-        <v/>
-      </c>
-      <c r="E11" s="8">
-        <f>E12+E17+E20</f>
-        <v/>
-      </c>
-      <c r="F11" s="8">
-        <f>F12+F17+F20</f>
-        <v/>
-      </c>
-      <c r="G11" s="8">
-        <f>G12+G17+G20</f>
-        <v/>
-      </c>
-      <c r="H11" s="8">
-        <f>H12+H17+H20</f>
-        <v/>
-      </c>
-      <c r="I11" s="8">
-        <f>I12+I17+I20</f>
-        <v/>
-      </c>
-      <c r="J11" s="8">
-        <f>J12+J17+J20</f>
-        <v/>
-      </c>
-      <c r="K11" s="8">
-        <f>K12+K17+K20</f>
-        <v/>
-      </c>
-      <c r="L11" s="8">
-        <f>L12+L17+L20</f>
-        <v/>
-      </c>
-      <c r="M11" s="8">
-        <f>M12+M17+M20</f>
-        <v/>
-      </c>
-      <c r="N11" s="8">
-        <f>N12+N17+N20</f>
-        <v/>
-      </c>
-      <c r="O11" s="8">
-        <f>O12+O17+O20</f>
-        <v/>
-      </c>
-      <c r="P11" s="8">
-        <f>SUM(D11:O11)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="8" t="n"/>
-    </row>
-    <row r="12" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8">
+        <f>D13+D18+D21</f>
+        <v/>
+      </c>
+      <c r="E12" s="8">
+        <f>E13+E18+E21</f>
+        <v/>
+      </c>
+      <c r="F12" s="8">
+        <f>F13+F18+F21</f>
+        <v/>
+      </c>
+      <c r="G12" s="8">
+        <f>G13+G18+G21</f>
+        <v/>
+      </c>
+      <c r="H12" s="8">
+        <f>H13+H18+H21</f>
+        <v/>
+      </c>
+      <c r="I12" s="8">
+        <f>I13+I18+I21</f>
+        <v/>
+      </c>
+      <c r="J12" s="8">
+        <f>J13+J18+J21</f>
+        <v/>
+      </c>
+      <c r="K12" s="8">
+        <f>K13+K18+K21</f>
+        <v/>
+      </c>
+      <c r="L12" s="8">
+        <f>L13+L18+L21</f>
+        <v/>
+      </c>
+      <c r="M12" s="8">
+        <f>M13+M18+M21</f>
+        <v/>
+      </c>
+      <c r="N12" s="8">
+        <f>N13+N18+N21</f>
+        <v/>
+      </c>
+      <c r="O12" s="8">
+        <f>O13+O18+O21</f>
+        <v/>
+      </c>
+      <c r="P12" s="8">
+        <f>SUM(D12:O12)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="8" t="n"/>
+    </row>
+    <row r="13" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Manufacturing</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10">
-        <f>SUM(D13:D14)+D15</f>
-        <v/>
-      </c>
-      <c r="E12" s="10">
-        <f>SUM(E13:E14)+E15</f>
-        <v/>
-      </c>
-      <c r="F12" s="10">
-        <f>SUM(F13:F14)+F15</f>
-        <v/>
-      </c>
-      <c r="G12" s="10">
-        <f>SUM(G13:G14)+G15</f>
-        <v/>
-      </c>
-      <c r="H12" s="10">
-        <f>SUM(H13:H14)+H15</f>
-        <v/>
-      </c>
-      <c r="I12" s="10">
-        <f>SUM(I13:I14)+I15</f>
-        <v/>
-      </c>
-      <c r="J12" s="10">
-        <f>SUM(J13:J14)+J15</f>
-        <v/>
-      </c>
-      <c r="K12" s="10">
-        <f>SUM(K13:K14)+K15</f>
-        <v/>
-      </c>
-      <c r="L12" s="10">
-        <f>SUM(L13:L14)+L15</f>
-        <v/>
-      </c>
-      <c r="M12" s="10">
-        <f>SUM(M13:M14)+M15</f>
-        <v/>
-      </c>
-      <c r="N12" s="10">
-        <f>SUM(N13:N14)+N15</f>
-        <v/>
-      </c>
-      <c r="O12" s="10">
-        <f>SUM(O13:O14)+O15</f>
-        <v/>
-      </c>
-      <c r="P12" s="10">
-        <f>SUM(D12:O12)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="10" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      JONDO</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="E13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="F13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="G13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="H13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="I13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="J13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="K13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="L13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="M13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="N13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="O13" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="P13" s="4">
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10">
+        <f>SUM(D14:D15)+D16</f>
+        <v/>
+      </c>
+      <c r="E13" s="10">
+        <f>SUM(E14:E15)+E16</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>SUM(F14:F15)+F16</f>
+        <v/>
+      </c>
+      <c r="G13" s="10">
+        <f>SUM(G14:G15)+G16</f>
+        <v/>
+      </c>
+      <c r="H13" s="10">
+        <f>SUM(H14:H15)+H16</f>
+        <v/>
+      </c>
+      <c r="I13" s="10">
+        <f>SUM(I14:I15)+I16</f>
+        <v/>
+      </c>
+      <c r="J13" s="10">
+        <f>SUM(J14:J15)+J16</f>
+        <v/>
+      </c>
+      <c r="K13" s="10">
+        <f>SUM(K14:K15)+K16</f>
+        <v/>
+      </c>
+      <c r="L13" s="10">
+        <f>SUM(L14:L15)+L16</f>
+        <v/>
+      </c>
+      <c r="M13" s="10">
+        <f>SUM(M14:M15)+M16</f>
+        <v/>
+      </c>
+      <c r="N13" s="10">
+        <f>SUM(N14:N15)+N16</f>
+        <v/>
+      </c>
+      <c r="O13" s="10">
+        <f>SUM(O14:O15)+O16</f>
+        <v/>
+      </c>
+      <c r="P13" s="10">
         <f>SUM(D13:O13)</f>
         <v/>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="Q13" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -1285,7 +1312,7 @@
     <row r="14" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">      TGI</t>
+          <t xml:space="preserve">      JONDO</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -1342,1124 +1369,1124 @@
         <f>SUM(D14:O14)</f>
         <v/>
       </c>
-      <c r="Q14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="12" customHeight="1">
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Consumo marcos</t>
+          <t xml:space="preserve">      TGI</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n">
-        <v>2658.96</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>1470.37</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>1496.84</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
+      <c r="D15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
+      <c r="E15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
+      <c r="F15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
+      <c r="H15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
+      <c r="I15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
+      <c r="J15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
+      <c r="K15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
+      <c r="L15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
+      <c r="M15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
+      <c r="N15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
+      <c r="O15" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A15))</f>
+        <v/>
+      </c>
       <c r="P15" s="4">
         <f>SUM(D15:O15)</f>
         <v/>
       </c>
       <c r="Q15" s="4" t="n"/>
     </row>
-    <row r="16" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="16" ht="12" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Consumo marcos</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n">
+        <v>2658.96</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>1470.37</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>1496.84</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4">
+        <f>SUM(D16:O16)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="4" t="n"/>
+    </row>
+    <row r="17" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % Manufacturing / sales</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12">
-        <f>IFERROR(D12/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E16" s="12">
-        <f>IFERROR(E12/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
-        <f>IFERROR(F12/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G16" s="12">
-        <f>IFERROR(G12/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H16" s="12">
-        <f>IFERROR(H12/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I16" s="12">
-        <f>IFERROR(I12/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J16" s="12">
-        <f>IFERROR(J12/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K16" s="12">
-        <f>IFERROR(K12/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L16" s="12">
-        <f>IFERROR(L12/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M16" s="12">
-        <f>IFERROR(M12/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N16" s="12">
-        <f>IFERROR(N12/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O16" s="12">
-        <f>IFERROR(O12/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P16" s="12">
-        <f>IFERROR(P12/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="12" t="n"/>
-    </row>
-    <row r="17" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11">
+        <f>IFERROR(D13/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="11">
+        <f>IFERROR(E13/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="11">
+        <f>IFERROR(F13/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="11">
+        <f>IFERROR(G13/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="11">
+        <f>IFERROR(H13/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I17" s="11">
+        <f>IFERROR(I13/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J17" s="11">
+        <f>IFERROR(J13/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="11">
+        <f>IFERROR(K13/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L17" s="11">
+        <f>IFERROR(L13/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M17" s="11">
+        <f>IFERROR(M13/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N17" s="11">
+        <f>IFERROR(N13/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O17" s="11">
+        <f>IFERROR(O13/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P17" s="11">
+        <f>IFERROR(P13/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="11" t="n"/>
+    </row>
+    <row r="18" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Logistics</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10">
-        <f>SUM(D18:D18)</f>
-        <v/>
-      </c>
-      <c r="E17" s="10">
-        <f>SUM(E18:E18)</f>
-        <v/>
-      </c>
-      <c r="F17" s="10">
-        <f>SUM(F18:F18)</f>
-        <v/>
-      </c>
-      <c r="G17" s="10">
-        <f>SUM(G18:G18)</f>
-        <v/>
-      </c>
-      <c r="H17" s="10">
-        <f>SUM(H18:H18)</f>
-        <v/>
-      </c>
-      <c r="I17" s="10">
-        <f>SUM(I18:I18)</f>
-        <v/>
-      </c>
-      <c r="J17" s="10">
-        <f>SUM(J18:J18)</f>
-        <v/>
-      </c>
-      <c r="K17" s="10">
-        <f>SUM(K18:K18)</f>
-        <v/>
-      </c>
-      <c r="L17" s="10">
-        <f>SUM(L18:L18)</f>
-        <v/>
-      </c>
-      <c r="M17" s="10">
-        <f>SUM(M18:M18)</f>
-        <v/>
-      </c>
-      <c r="N17" s="10">
-        <f>SUM(N18:N18)</f>
-        <v/>
-      </c>
-      <c r="O17" s="10">
-        <f>SUM(O18:O18)</f>
-        <v/>
-      </c>
-      <c r="P17" s="10">
-        <f>SUM(D17:O17)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="10" t="inlineStr">
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10">
+        <f>SUM(D19:D19)</f>
+        <v/>
+      </c>
+      <c r="E18" s="10">
+        <f>SUM(E19:E19)</f>
+        <v/>
+      </c>
+      <c r="F18" s="10">
+        <f>SUM(F19:F19)</f>
+        <v/>
+      </c>
+      <c r="G18" s="10">
+        <f>SUM(G19:G19)</f>
+        <v/>
+      </c>
+      <c r="H18" s="10">
+        <f>SUM(H19:H19)</f>
+        <v/>
+      </c>
+      <c r="I18" s="10">
+        <f>SUM(I19:I19)</f>
+        <v/>
+      </c>
+      <c r="J18" s="10">
+        <f>SUM(J19:J19)</f>
+        <v/>
+      </c>
+      <c r="K18" s="10">
+        <f>SUM(K19:K19)</f>
+        <v/>
+      </c>
+      <c r="L18" s="10">
+        <f>SUM(L19:L19)</f>
+        <v/>
+      </c>
+      <c r="M18" s="10">
+        <f>SUM(M19:M19)</f>
+        <v/>
+      </c>
+      <c r="N18" s="10">
+        <f>SUM(N19:N19)</f>
+        <v/>
+      </c>
+      <c r="O18" s="10">
+        <f>SUM(O19:O19)</f>
+        <v/>
+      </c>
+      <c r="P18" s="10">
+        <f>SUM(D18:O18)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="18" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t xml:space="preserve">      TGI</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="E18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="F18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="G18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="H18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="I18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="J18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="K18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="L18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="M18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="N18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="O18" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A18))</f>
-        <v/>
-      </c>
-      <c r="P18" s="4">
-        <f>SUM(D18:O18)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="E19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="F19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="H19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="I19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="J19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="K19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="L19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="M19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="N19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="O19" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
+        <v/>
+      </c>
+      <c r="P19" s="4">
+        <f>SUM(D19:O19)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="19" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="20" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % Logistics / sales</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12">
-        <f>IFERROR(D17/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E19" s="12">
-        <f>IFERROR(E17/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
-        <f>IFERROR(F17/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="12">
-        <f>IFERROR(G17/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H19" s="12">
-        <f>IFERROR(H17/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I19" s="12">
-        <f>IFERROR(I17/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J19" s="12">
-        <f>IFERROR(J17/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K19" s="12">
-        <f>IFERROR(K17/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L19" s="12">
-        <f>IFERROR(L17/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M19" s="12">
-        <f>IFERROR(M17/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N19" s="12">
-        <f>IFERROR(N17/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O19" s="12">
-        <f>IFERROR(O17/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P19" s="12">
-        <f>IFERROR(P17/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="12" t="n"/>
-    </row>
-    <row r="20" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11">
+        <f>IFERROR(D18/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E20" s="11">
+        <f>IFERROR(E18/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="11">
+        <f>IFERROR(F18/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IFERROR(G18/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="11">
+        <f>IFERROR(H18/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I20" s="11">
+        <f>IFERROR(I18/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J20" s="11">
+        <f>IFERROR(J18/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="11">
+        <f>IFERROR(K18/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L20" s="11">
+        <f>IFERROR(L18/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M20" s="11">
+        <f>IFERROR(M18/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N20" s="11">
+        <f>IFERROR(N18/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O20" s="11">
+        <f>IFERROR(O18/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P20" s="11">
+        <f>IFERROR(P18/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="11" t="n"/>
+    </row>
+    <row r="21" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Payment fees</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10">
-        <f>SUM(D21:D21)</f>
-        <v/>
-      </c>
-      <c r="E20" s="10">
-        <f>SUM(E21:E21)</f>
-        <v/>
-      </c>
-      <c r="F20" s="10">
-        <f>SUM(F21:F21)</f>
-        <v/>
-      </c>
-      <c r="G20" s="10">
-        <f>SUM(G21:G21)</f>
-        <v/>
-      </c>
-      <c r="H20" s="10">
-        <f>SUM(H21:H21)</f>
-        <v/>
-      </c>
-      <c r="I20" s="10">
-        <f>SUM(I21:I21)</f>
-        <v/>
-      </c>
-      <c r="J20" s="10">
-        <f>SUM(J21:J21)</f>
-        <v/>
-      </c>
-      <c r="K20" s="10">
-        <f>SUM(K21:K21)</f>
-        <v/>
-      </c>
-      <c r="L20" s="10">
-        <f>SUM(L21:L21)</f>
-        <v/>
-      </c>
-      <c r="M20" s="10">
-        <f>SUM(M21:M21)</f>
-        <v/>
-      </c>
-      <c r="N20" s="10">
-        <f>SUM(N21:N21)</f>
-        <v/>
-      </c>
-      <c r="O20" s="10">
-        <f>SUM(O21:O21)</f>
-        <v/>
-      </c>
-      <c r="P20" s="10">
-        <f>SUM(D20:O20)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="10" t="inlineStr">
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10">
+        <f>SUM(D22:D22)</f>
+        <v/>
+      </c>
+      <c r="E21" s="10">
+        <f>SUM(E22:E22)</f>
+        <v/>
+      </c>
+      <c r="F21" s="10">
+        <f>SUM(F22:F22)</f>
+        <v/>
+      </c>
+      <c r="G21" s="10">
+        <f>SUM(G22:G22)</f>
+        <v/>
+      </c>
+      <c r="H21" s="10">
+        <f>SUM(H22:H22)</f>
+        <v/>
+      </c>
+      <c r="I21" s="10">
+        <f>SUM(I22:I22)</f>
+        <v/>
+      </c>
+      <c r="J21" s="10">
+        <f>SUM(J22:J22)</f>
+        <v/>
+      </c>
+      <c r="K21" s="10">
+        <f>SUM(K22:K22)</f>
+        <v/>
+      </c>
+      <c r="L21" s="10">
+        <f>SUM(L22:L22)</f>
+        <v/>
+      </c>
+      <c r="M21" s="10">
+        <f>SUM(M22:M22)</f>
+        <v/>
+      </c>
+      <c r="N21" s="10">
+        <f>SUM(N22:N22)</f>
+        <v/>
+      </c>
+      <c r="O21" s="10">
+        <f>SUM(O22:O22)</f>
+        <v/>
+      </c>
+      <c r="P21" s="10">
+        <f>SUM(D21:O21)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="21" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">      SHOPIFY</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,D$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="E21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,E$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="F21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,F$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="G21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,G$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="H21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,H$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="I21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,I$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="J21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,J$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="K21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,K$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="L21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,L$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="M21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,M$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="N21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,N$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="O21" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,O$1,'g-payment-fees-inc'!$C:$C,TRIM($A21))</f>
-        <v/>
-      </c>
-      <c r="P21" s="4">
-        <f>SUM(D21:O21)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="12" customHeight="1">
       <c r="B22" s="4" t="n"/>
       <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="4" t="n"/>
+      <c r="D22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,D$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
+      <c r="E22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,E$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
+      <c r="F22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,F$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,G$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
+      <c r="H22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,H$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
+      <c r="I22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,I$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,J$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,K$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
+      <c r="L22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,L$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
+      <c r="M22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,M$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
+      <c r="N22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,N$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
+      <c r="O22" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,O$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
+        <v/>
+      </c>
       <c r="P22" s="4">
         <f>SUM(D22:O22)</f>
         <v/>
       </c>
-      <c r="Q22" s="4" t="n"/>
-    </row>
-    <row r="23" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="12" customHeight="1">
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4">
+        <f>SUM(D23:O23)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="4" t="n"/>
+    </row>
+    <row r="24" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % Payment fees / sales</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12">
-        <f>IFERROR(D20/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E23" s="12">
-        <f>IFERROR(E20/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F23" s="12">
-        <f>IFERROR(F20/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G23" s="12">
-        <f>IFERROR(G20/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H23" s="12">
-        <f>IFERROR(H20/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I23" s="12">
-        <f>IFERROR(I20/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J23" s="12">
-        <f>IFERROR(J20/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K23" s="12">
-        <f>IFERROR(K20/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L23" s="12">
-        <f>IFERROR(L20/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M23" s="12">
-        <f>IFERROR(M20/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N23" s="12">
-        <f>IFERROR(N20/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O23" s="12">
-        <f>IFERROR(O20/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P23" s="12">
-        <f>IFERROR(P20/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q23" s="12" t="n"/>
-    </row>
-    <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="n"/>
-      <c r="P24" s="4">
-        <f>SUM(D24:O24)</f>
-        <v/>
-      </c>
-      <c r="Q24" s="4" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11">
+        <f>IFERROR(D21/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
+        <f>IFERROR(E21/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="11">
+        <f>IFERROR(F21/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="11">
+        <f>IFERROR(G21/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="11">
+        <f>IFERROR(H21/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I24" s="11">
+        <f>IFERROR(I21/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J24" s="11">
+        <f>IFERROR(J21/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="11">
+        <f>IFERROR(K21/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L24" s="11">
+        <f>IFERROR(L21/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M24" s="11">
+        <f>IFERROR(M21/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N24" s="11">
+        <f>IFERROR(N21/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O24" s="11">
+        <f>IFERROR(O21/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P24" s="11">
+        <f>IFERROR(P21/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q24" s="11" t="n"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4">
+        <f>SUM(D25:O25)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="12" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>GROSS MARGIN (SALES-MANUFACTURING)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14">
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13">
+        <f>D5-D13</f>
+        <v/>
+      </c>
+      <c r="E26" s="13">
+        <f>E5-E13</f>
+        <v/>
+      </c>
+      <c r="F26" s="13">
+        <f>F5-F13</f>
+        <v/>
+      </c>
+      <c r="G26" s="13">
+        <f>G5-G13</f>
+        <v/>
+      </c>
+      <c r="H26" s="13">
+        <f>H5-H13</f>
+        <v/>
+      </c>
+      <c r="I26" s="13">
+        <f>I5-I13</f>
+        <v/>
+      </c>
+      <c r="J26" s="13">
+        <f>J5-J13</f>
+        <v/>
+      </c>
+      <c r="K26" s="13">
+        <f>K5-K13</f>
+        <v/>
+      </c>
+      <c r="L26" s="13">
+        <f>L5-L13</f>
+        <v/>
+      </c>
+      <c r="M26" s="13">
+        <f>M5-M13</f>
+        <v/>
+      </c>
+      <c r="N26" s="13">
+        <f>N5-N13</f>
+        <v/>
+      </c>
+      <c r="O26" s="13">
+        <f>O5-O13</f>
+        <v/>
+      </c>
+      <c r="P26" s="13">
+        <f>SUM(D26:O26)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="13" t="n"/>
+    </row>
+    <row r="27" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>% gross margin</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11">
+        <f>IFERROR(D26/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E27" s="11">
+        <f>IFERROR(E26/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="11">
+        <f>IFERROR(F26/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="11">
+        <f>IFERROR(G26/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="11">
+        <f>IFERROR(H26/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I27" s="11">
+        <f>IFERROR(I26/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J27" s="11">
+        <f>IFERROR(J26/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="11">
+        <f>IFERROR(K26/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L27" s="11">
+        <f>IFERROR(L26/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="11">
+        <f>IFERROR(M26/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N27" s="11">
+        <f>IFERROR(N26/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O27" s="11">
+        <f>IFERROR(O26/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P27" s="11">
+        <f>IFERROR(P26/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="11" t="n"/>
+    </row>
+    <row r="28" ht="12" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Contributive margin (product sales-COGS)</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13">
         <f>D5-D12</f>
         <v/>
       </c>
-      <c r="E25" s="14">
+      <c r="E28" s="13">
         <f>E5-E12</f>
         <v/>
       </c>
-      <c r="F25" s="14">
+      <c r="F28" s="13">
         <f>F5-F12</f>
         <v/>
       </c>
-      <c r="G25" s="14">
+      <c r="G28" s="13">
         <f>G5-G12</f>
         <v/>
       </c>
-      <c r="H25" s="14">
+      <c r="H28" s="13">
         <f>H5-H12</f>
         <v/>
       </c>
-      <c r="I25" s="14">
+      <c r="I28" s="13">
         <f>I5-I12</f>
         <v/>
       </c>
-      <c r="J25" s="14">
+      <c r="J28" s="13">
         <f>J5-J12</f>
         <v/>
       </c>
-      <c r="K25" s="14">
+      <c r="K28" s="13">
         <f>K5-K12</f>
         <v/>
       </c>
-      <c r="L25" s="14">
+      <c r="L28" s="13">
         <f>L5-L12</f>
         <v/>
       </c>
-      <c r="M25" s="14">
+      <c r="M28" s="13">
         <f>M5-M12</f>
         <v/>
       </c>
-      <c r="N25" s="14">
+      <c r="N28" s="13">
         <f>N5-N12</f>
         <v/>
       </c>
-      <c r="O25" s="14">
+      <c r="O28" s="13">
         <f>O5-O12</f>
         <v/>
       </c>
-      <c r="P25" s="14">
-        <f>SUM(D25:O25)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="14" t="n"/>
-    </row>
-    <row r="26" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>% GROSS MARGIN</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12">
-        <f>IFERROR(D25/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E26" s="12">
-        <f>IFERROR(E25/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F26" s="12">
-        <f>IFERROR(F25/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G26" s="12">
-        <f>IFERROR(G25/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H26" s="12">
-        <f>IFERROR(H25/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I26" s="12">
-        <f>IFERROR(I25/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J26" s="12">
-        <f>IFERROR(J25/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K26" s="12">
-        <f>IFERROR(K25/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L26" s="12">
-        <f>IFERROR(L25/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M26" s="12">
-        <f>IFERROR(M25/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N26" s="12">
-        <f>IFERROR(N25/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O26" s="12">
-        <f>IFERROR(O25/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P26" s="12">
-        <f>IFERROR(P25/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="12" t="n"/>
-    </row>
-    <row r="27" ht="12" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>CONTRIBUTIVE MARGIN (TURNOVER-COGS)</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14">
-        <f>D4-D11</f>
-        <v/>
-      </c>
-      <c r="E27" s="14">
-        <f>E4-E11</f>
-        <v/>
-      </c>
-      <c r="F27" s="14">
-        <f>F4-F11</f>
-        <v/>
-      </c>
-      <c r="G27" s="14">
-        <f>G4-G11</f>
-        <v/>
-      </c>
-      <c r="H27" s="14">
-        <f>H4-H11</f>
-        <v/>
-      </c>
-      <c r="I27" s="14">
-        <f>I4-I11</f>
-        <v/>
-      </c>
-      <c r="J27" s="14">
-        <f>J4-J11</f>
-        <v/>
-      </c>
-      <c r="K27" s="14">
-        <f>K4-K11</f>
-        <v/>
-      </c>
-      <c r="L27" s="14">
-        <f>L4-L11</f>
-        <v/>
-      </c>
-      <c r="M27" s="14">
-        <f>M4-M11</f>
-        <v/>
-      </c>
-      <c r="N27" s="14">
-        <f>N4-N11</f>
-        <v/>
-      </c>
-      <c r="O27" s="14">
-        <f>O4-O11</f>
-        <v/>
-      </c>
-      <c r="P27" s="14">
-        <f>SUM(D27:O27)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="14" t="n"/>
-    </row>
-    <row r="28" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>% CONTRIBUTIVE MARGIN</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12">
-        <f>IFERROR(D27/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E28" s="12">
-        <f>IFERROR(E27/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F28" s="12">
-        <f>IFERROR(F27/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G28" s="12">
-        <f>IFERROR(G27/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H28" s="12">
-        <f>IFERROR(H27/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I28" s="12">
-        <f>IFERROR(I27/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J28" s="12">
-        <f>IFERROR(J27/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K28" s="12">
-        <f>IFERROR(K27/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L28" s="12">
-        <f>IFERROR(L27/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M28" s="12">
-        <f>IFERROR(M27/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N28" s="12">
-        <f>IFERROR(N27/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O28" s="12">
-        <f>IFERROR(O27/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P28" s="12">
-        <f>IFERROR(P27/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="n"/>
-      <c r="M29" s="4" t="n"/>
-      <c r="N29" s="4" t="n"/>
-      <c r="O29" s="4" t="n"/>
-      <c r="P29" s="4">
-        <f>SUM(D29:O29)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="4" t="n"/>
-    </row>
-    <row r="30" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="P28" s="13">
+        <f>SUM(D28:O28)</f>
+        <v/>
+      </c>
+      <c r="Q28" s="13" t="n"/>
+    </row>
+    <row r="29" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>% contributive margin</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11">
+        <f>IFERROR(D28/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E29" s="11">
+        <f>IFERROR(E28/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F29" s="11">
+        <f>IFERROR(F28/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="11">
+        <f>IFERROR(G28/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="11">
+        <f>IFERROR(H28/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I29" s="11">
+        <f>IFERROR(I28/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J29" s="11">
+        <f>IFERROR(J28/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="11">
+        <f>IFERROR(K28/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="11">
+        <f>IFERROR(L28/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="11">
+        <f>IFERROR(M28/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N29" s="11">
+        <f>IFERROR(N28/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O29" s="11">
+        <f>IFERROR(O28/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P29" s="11">
+        <f>IFERROR(P28/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="12" customHeight="1">
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4">
+        <f>SUM(D30:O30)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="4" t="n"/>
+    </row>
+    <row r="31" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Opex</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8">
-        <f>D31+D33+D39+D41</f>
-        <v/>
-      </c>
-      <c r="E30" s="8">
-        <f>E31+E33+E39+E41</f>
-        <v/>
-      </c>
-      <c r="F30" s="8">
-        <f>F31+F33+F39+F41</f>
-        <v/>
-      </c>
-      <c r="G30" s="8">
-        <f>G31+G33+G39+G41</f>
-        <v/>
-      </c>
-      <c r="H30" s="8">
-        <f>H31+H33+H39+H41</f>
-        <v/>
-      </c>
-      <c r="I30" s="8">
-        <f>I31+I33+I39+I41</f>
-        <v/>
-      </c>
-      <c r="J30" s="8">
-        <f>J31+J33+J39+J41</f>
-        <v/>
-      </c>
-      <c r="K30" s="8">
-        <f>K31+K33+K39+K41</f>
-        <v/>
-      </c>
-      <c r="L30" s="8">
-        <f>L31+L33+L39+L41</f>
-        <v/>
-      </c>
-      <c r="M30" s="8">
-        <f>M31+M33+M39+M41</f>
-        <v/>
-      </c>
-      <c r="N30" s="8">
-        <f>N31+N33+N39+N41</f>
-        <v/>
-      </c>
-      <c r="O30" s="8">
-        <f>O31+O33+O39+O41</f>
-        <v/>
-      </c>
-      <c r="P30" s="8">
-        <f>SUM(D30:O30)</f>
-        <v/>
-      </c>
-      <c r="Q30" s="8" t="n"/>
-    </row>
-    <row r="31" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8">
+        <f>D32+D34+D41+D43</f>
+        <v/>
+      </c>
+      <c r="E31" s="8">
+        <f>E32+E34+E41+E43</f>
+        <v/>
+      </c>
+      <c r="F31" s="8">
+        <f>F32+F34+F41+F43</f>
+        <v/>
+      </c>
+      <c r="G31" s="8">
+        <f>G32+G34+G41+G43</f>
+        <v/>
+      </c>
+      <c r="H31" s="8">
+        <f>H32+H34+H41+H43</f>
+        <v/>
+      </c>
+      <c r="I31" s="8">
+        <f>I32+I34+I41+I43</f>
+        <v/>
+      </c>
+      <c r="J31" s="8">
+        <f>J32+J34+J41+J43</f>
+        <v/>
+      </c>
+      <c r="K31" s="8">
+        <f>K32+K34+K41+K43</f>
+        <v/>
+      </c>
+      <c r="L31" s="8">
+        <f>L32+L34+L41+L43</f>
+        <v/>
+      </c>
+      <c r="M31" s="8">
+        <f>M32+M34+M41+M43</f>
+        <v/>
+      </c>
+      <c r="N31" s="8">
+        <f>N32+N34+N41+N43</f>
+        <v/>
+      </c>
+      <c r="O31" s="8">
+        <f>O32+O34+O41+O43</f>
+        <v/>
+      </c>
+      <c r="P31" s="8">
+        <f>SUM(D31:O31)</f>
+        <v/>
+      </c>
+      <c r="Q31" s="8" t="n"/>
+    </row>
+    <row r="32" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Shared services</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10">
-        <f>SUM(D32:D32)</f>
-        <v/>
-      </c>
-      <c r="E31" s="10">
-        <f>SUM(E32:E32)</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
-        <f>SUM(F32:F32)</f>
-        <v/>
-      </c>
-      <c r="G31" s="10">
-        <f>SUM(G32:G32)</f>
-        <v/>
-      </c>
-      <c r="H31" s="10">
-        <f>SUM(H32:H32)</f>
-        <v/>
-      </c>
-      <c r="I31" s="10">
-        <f>SUM(I32:I32)</f>
-        <v/>
-      </c>
-      <c r="J31" s="10">
-        <f>SUM(J32:J32)</f>
-        <v/>
-      </c>
-      <c r="K31" s="10">
-        <f>SUM(K32:K32)</f>
-        <v/>
-      </c>
-      <c r="L31" s="10">
-        <f>SUM(L32:L32)</f>
-        <v/>
-      </c>
-      <c r="M31" s="10">
-        <f>SUM(M32:M32)</f>
-        <v/>
-      </c>
-      <c r="N31" s="10">
-        <f>SUM(N32:N32)</f>
-        <v/>
-      </c>
-      <c r="O31" s="10">
-        <f>SUM(O32:O32)</f>
-        <v/>
-      </c>
-      <c r="P31" s="10">
-        <f>SUM(D31:O31)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="10" t="inlineStr">
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10">
+        <f>SUM(D33:D33)</f>
+        <v/>
+      </c>
+      <c r="E32" s="10">
+        <f>SUM(E33:E33)</f>
+        <v/>
+      </c>
+      <c r="F32" s="10">
+        <f>SUM(F33:F33)</f>
+        <v/>
+      </c>
+      <c r="G32" s="10">
+        <f>SUM(G33:G33)</f>
+        <v/>
+      </c>
+      <c r="H32" s="10">
+        <f>SUM(H33:H33)</f>
+        <v/>
+      </c>
+      <c r="I32" s="10">
+        <f>SUM(I33:I33)</f>
+        <v/>
+      </c>
+      <c r="J32" s="10">
+        <f>SUM(J33:J33)</f>
+        <v/>
+      </c>
+      <c r="K32" s="10">
+        <f>SUM(K33:K33)</f>
+        <v/>
+      </c>
+      <c r="L32" s="10">
+        <f>SUM(L33:L33)</f>
+        <v/>
+      </c>
+      <c r="M32" s="10">
+        <f>SUM(M33:M33)</f>
+        <v/>
+      </c>
+      <c r="N32" s="10">
+        <f>SUM(N33:N33)</f>
+        <v/>
+      </c>
+      <c r="O32" s="10">
+        <f>SUM(O33:O33)</f>
+        <v/>
+      </c>
+      <c r="P32" s="10">
+        <f>SUM(D32:O32)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="32" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t xml:space="preserve">      SHAREDSERVICESSL</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="E32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="F32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="G32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="H32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="I32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="J32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="K32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="L32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="M32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="N32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="O32" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A32))</f>
-        <v/>
-      </c>
-      <c r="P32" s="4">
-        <f>SUM(D32:O32)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="E33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="F33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="G33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="H33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="I33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="J33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="K33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="L33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="M33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="N33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="O33" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
+        <v/>
+      </c>
+      <c r="P33" s="4">
+        <f>SUM(D33:O33)</f>
+        <v/>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="33" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="34" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Administration</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10">
-        <f>SUM(D34:D38)</f>
-        <v/>
-      </c>
-      <c r="E33" s="10">
-        <f>SUM(E34:E38)</f>
-        <v/>
-      </c>
-      <c r="F33" s="10">
-        <f>SUM(F34:F38)</f>
-        <v/>
-      </c>
-      <c r="G33" s="10">
-        <f>SUM(G34:G38)</f>
-        <v/>
-      </c>
-      <c r="H33" s="10">
-        <f>SUM(H34:H38)</f>
-        <v/>
-      </c>
-      <c r="I33" s="10">
-        <f>SUM(I34:I38)</f>
-        <v/>
-      </c>
-      <c r="J33" s="10">
-        <f>SUM(J34:J38)</f>
-        <v/>
-      </c>
-      <c r="K33" s="10">
-        <f>SUM(K34:K38)</f>
-        <v/>
-      </c>
-      <c r="L33" s="10">
-        <f>SUM(L34:L38)</f>
-        <v/>
-      </c>
-      <c r="M33" s="10">
-        <f>SUM(M34:M38)</f>
-        <v/>
-      </c>
-      <c r="N33" s="10">
-        <f>SUM(N34:N38)</f>
-        <v/>
-      </c>
-      <c r="O33" s="10">
-        <f>SUM(O34:O38)</f>
-        <v/>
-      </c>
-      <c r="P33" s="10">
-        <f>SUM(D33:O33)</f>
-        <v/>
-      </c>
-      <c r="Q33" s="10" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      CONTINUUM</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="E34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="F34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="G34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="H34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="I34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="K34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="L34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="M34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="N34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="O34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="P34" s="4">
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10">
+        <f>SUM(D35:D40)</f>
+        <v/>
+      </c>
+      <c r="E34" s="10">
+        <f>SUM(E35:E40)</f>
+        <v/>
+      </c>
+      <c r="F34" s="10">
+        <f>SUM(F35:F40)</f>
+        <v/>
+      </c>
+      <c r="G34" s="10">
+        <f>SUM(G35:G40)</f>
+        <v/>
+      </c>
+      <c r="H34" s="10">
+        <f>SUM(H35:H40)</f>
+        <v/>
+      </c>
+      <c r="I34" s="10">
+        <f>SUM(I35:I40)</f>
+        <v/>
+      </c>
+      <c r="J34" s="10">
+        <f>SUM(J35:J40)</f>
+        <v/>
+      </c>
+      <c r="K34" s="10">
+        <f>SUM(K35:K40)</f>
+        <v/>
+      </c>
+      <c r="L34" s="10">
+        <f>SUM(L35:L40)</f>
+        <v/>
+      </c>
+      <c r="M34" s="10">
+        <f>SUM(M35:M40)</f>
+        <v/>
+      </c>
+      <c r="N34" s="10">
+        <f>SUM(N35:N40)</f>
+        <v/>
+      </c>
+      <c r="O34" s="10">
+        <f>SUM(O35:O40)</f>
+        <v/>
+      </c>
+      <c r="P34" s="10">
         <f>SUM(D34:O34)</f>
         <v/>
       </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="Q34" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -2468,7 +2495,7 @@
     <row r="35" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">      HUSHED</t>
+          <t xml:space="preserve">      CONTINUUM</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -2525,12 +2552,16 @@
         <f>SUM(D35:O35)</f>
         <v/>
       </c>
-      <c r="Q35" s="4" t="n"/>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="36" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">      IPOSTAL</t>
+          <t xml:space="preserve">      DELAWARE</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -2592,7 +2623,7 @@
     <row r="37" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">      QUICKBOOKS</t>
+          <t xml:space="preserve">      HUSHED</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -2654,7 +2685,7 @@
     <row r="38" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">      REGUS</t>
+          <t xml:space="preserve">      IPOSTAL</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -2713,192 +2744,184 @@
       </c>
       <c r="Q38" s="4" t="n"/>
     </row>
-    <row r="39" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Technology</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10">
-        <f>SUM(D40:D40)</f>
-        <v/>
-      </c>
-      <c r="E39" s="10">
-        <f>SUM(E40:E40)</f>
-        <v/>
-      </c>
-      <c r="F39" s="10">
-        <f>SUM(F40:F40)</f>
-        <v/>
-      </c>
-      <c r="G39" s="10">
-        <f>SUM(G40:G40)</f>
-        <v/>
-      </c>
-      <c r="H39" s="10">
-        <f>SUM(H40:H40)</f>
-        <v/>
-      </c>
-      <c r="I39" s="10">
-        <f>SUM(I40:I40)</f>
-        <v/>
-      </c>
-      <c r="J39" s="10">
-        <f>SUM(J40:J40)</f>
-        <v/>
-      </c>
-      <c r="K39" s="10">
-        <f>SUM(K40:K40)</f>
-        <v/>
-      </c>
-      <c r="L39" s="10">
-        <f>SUM(L40:L40)</f>
-        <v/>
-      </c>
-      <c r="M39" s="10">
-        <f>SUM(M40:M40)</f>
-        <v/>
-      </c>
-      <c r="N39" s="10">
-        <f>SUM(N40:N40)</f>
-        <v/>
-      </c>
-      <c r="O39" s="10">
-        <f>SUM(O40:O40)</f>
-        <v/>
-      </c>
-      <c r="P39" s="10">
+    <row r="39" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      QUICKBOOKS</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="E39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="F39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="G39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="H39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="I39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="J39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="K39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="L39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="M39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="N39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="O39" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="P39" s="4">
         <f>SUM(D39:O39)</f>
         <v/>
       </c>
-      <c r="Q39" s="10" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="Q39" s="4" t="n"/>
     </row>
     <row r="40" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">      REVER</t>
+          <t xml:space="preserve">      REGUS</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
       <c r="C40" s="4" t="n"/>
       <c r="D40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="E40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="F40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="G40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="H40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="I40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="J40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="K40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="L40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="M40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="N40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="O40" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A40))</f>
         <v/>
       </c>
       <c r="P40" s="4">
         <f>SUM(D40:O40)</f>
         <v/>
       </c>
-      <c r="Q40" s="4" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="Q40" s="4" t="n"/>
     </row>
     <row r="41" hidden="1" outlineLevel="2" ht="12" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Otros gastos</t>
+          <t xml:space="preserve">    Technology</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(D42:D42)</f>
         <v/>
       </c>
       <c r="E41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(E42:E42)</f>
         <v/>
       </c>
       <c r="F41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(F42:F42)</f>
         <v/>
       </c>
       <c r="G41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(G42:G42)</f>
         <v/>
       </c>
       <c r="H41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(H42:H42)</f>
         <v/>
       </c>
       <c r="I41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(I42:I42)</f>
         <v/>
       </c>
       <c r="J41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(J42:J42)</f>
         <v/>
       </c>
       <c r="K41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(K42:K42)</f>
         <v/>
       </c>
       <c r="L41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(L42:L42)</f>
         <v/>
       </c>
       <c r="M41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(M42:M42)</f>
         <v/>
       </c>
       <c r="N41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(N42:N42)</f>
         <v/>
       </c>
       <c r="O41" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <f>SUM(O42:O42)</f>
         <v/>
       </c>
       <c r="P41" s="10">
@@ -2911,249 +2934,316 @@
         </is>
       </c>
     </row>
-    <row r="42" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Diferencias divisas</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="10" t="n"/>
-      <c r="I42" s="10" t="n"/>
-      <c r="J42" s="10" t="n"/>
-      <c r="K42" s="10" t="n"/>
-      <c r="L42" s="10" t="n"/>
-      <c r="M42" s="10" t="n"/>
-      <c r="N42" s="10" t="n"/>
-      <c r="O42" s="10" t="n"/>
-      <c r="P42" s="10">
+    <row r="42" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      REVER</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="E42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="F42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="G42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="H42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="I42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="J42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="K42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="L42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="M42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="N42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="O42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="P42" s="4">
         <f>SUM(D42:O42)</f>
         <v/>
       </c>
-      <c r="Q42" s="10" t="n"/>
-    </row>
-    <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-      <c r="L43" s="4" t="n"/>
-      <c r="M43" s="4" t="n"/>
-      <c r="N43" s="4" t="n"/>
-      <c r="O43" s="4" t="n"/>
-      <c r="P43" s="4">
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Uncategorized Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="E43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="G43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="H43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="I43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="J43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="K43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="L43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="M43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="N43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="O43" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="P43" s="10">
         <f>SUM(D43:O43)</f>
         <v/>
       </c>
-      <c r="Q43" s="4" t="n"/>
-    </row>
-    <row r="44" ht="12" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="10" t="n"/>
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="n"/>
+      <c r="P44" s="10">
+        <f>SUM(D44:O44)</f>
+        <v/>
+      </c>
+      <c r="Q44" s="10" t="n"/>
+    </row>
+    <row r="45" ht="12" customHeight="1">
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="n"/>
+      <c r="P45" s="4">
+        <f>SUM(D45:O45)</f>
+        <v/>
+      </c>
+      <c r="Q45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="12" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>PROFIT</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n"/>
-      <c r="C44" s="14" t="n"/>
-      <c r="D44" s="14">
-        <f>D4-D11-D30-D42</f>
-        <v/>
-      </c>
-      <c r="E44" s="14">
-        <f>E4-E11-E30-E42</f>
-        <v/>
-      </c>
-      <c r="F44" s="14">
-        <f>F4-F11-F30-F42</f>
-        <v/>
-      </c>
-      <c r="G44" s="14">
-        <f>G4-G11-G30-G42</f>
-        <v/>
-      </c>
-      <c r="H44" s="14">
-        <f>H4-H11-H30-H42</f>
-        <v/>
-      </c>
-      <c r="I44" s="14">
-        <f>I4-I11-I30-I42</f>
-        <v/>
-      </c>
-      <c r="J44" s="14">
-        <f>J4-J11-J30-J42</f>
-        <v/>
-      </c>
-      <c r="K44" s="14">
-        <f>K4-K11-K30-K42</f>
-        <v/>
-      </c>
-      <c r="L44" s="14">
-        <f>L4-L11-L30-L42</f>
-        <v/>
-      </c>
-      <c r="M44" s="14">
-        <f>M4-M11-M30-M42</f>
-        <v/>
-      </c>
-      <c r="N44" s="14">
-        <f>N4-N11-N30-N42</f>
-        <v/>
-      </c>
-      <c r="O44" s="14">
-        <f>O4-O11-O30-O42</f>
-        <v/>
-      </c>
-      <c r="P44" s="14">
-        <f>SUM(D44:O44)</f>
-        <v/>
-      </c>
-      <c r="Q44" s="14" t="n"/>
-    </row>
-    <row r="45" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>% Profit / product sales</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12">
-        <f>IFERROR(D44/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E45" s="12">
-        <f>IFERROR(E44/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F45" s="12">
-        <f>IFERROR(F44/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G45" s="12">
-        <f>IFERROR(G44/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H45" s="12">
-        <f>IFERROR(H44/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I45" s="12">
-        <f>IFERROR(I44/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J45" s="12">
-        <f>IFERROR(J44/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K45" s="12">
-        <f>IFERROR(K44/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L45" s="12">
-        <f>IFERROR(L44/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M45" s="12">
-        <f>IFERROR(M44/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N45" s="12">
-        <f>IFERROR(N44/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O45" s="12">
-        <f>IFERROR(O44/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P45" s="12">
-        <f>IFERROR(P44/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q45" s="12" t="n"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-      <c r="L46" s="4" t="n"/>
-      <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="n"/>
-      <c r="O46" s="4" t="n"/>
-      <c r="P46" s="4" t="n"/>
-      <c r="Q46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>Stock inicial marcos</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n">
-        <v>15764.34</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>13105.38</v>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>11635.01</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>10232.85</v>
-      </c>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="n"/>
-      <c r="L47" s="4" t="n"/>
-      <c r="M47" s="4" t="n"/>
-      <c r="N47" s="4" t="n"/>
-      <c r="O47" s="4" t="n"/>
-      <c r="P47" s="4">
-        <f>SUM(D47:O47)</f>
-        <v/>
-      </c>
-      <c r="Q47" s="4" t="n"/>
+      <c r="B46" s="13" t="n"/>
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="13">
+        <f>D4-D12-D31-D44</f>
+        <v/>
+      </c>
+      <c r="E46" s="13">
+        <f>E4-E12-E31-E44</f>
+        <v/>
+      </c>
+      <c r="F46" s="13">
+        <f>F4-F12-F31-F44</f>
+        <v/>
+      </c>
+      <c r="G46" s="13">
+        <f>G4-G12-G31-G44</f>
+        <v/>
+      </c>
+      <c r="H46" s="13">
+        <f>H4-H12-H31-H44</f>
+        <v/>
+      </c>
+      <c r="I46" s="13">
+        <f>I4-I12-I31-I44</f>
+        <v/>
+      </c>
+      <c r="J46" s="13">
+        <f>J4-J12-J31-J44</f>
+        <v/>
+      </c>
+      <c r="K46" s="13">
+        <f>K4-K12-K31-K44</f>
+        <v/>
+      </c>
+      <c r="L46" s="13">
+        <f>L4-L12-L31-L44</f>
+        <v/>
+      </c>
+      <c r="M46" s="13">
+        <f>M4-M12-M31-M44</f>
+        <v/>
+      </c>
+      <c r="N46" s="13">
+        <f>N4-N12-N31-N44</f>
+        <v/>
+      </c>
+      <c r="O46" s="13">
+        <f>O4-O12-O31-O44</f>
+        <v/>
+      </c>
+      <c r="P46" s="13">
+        <f>SUM(D46:O46)</f>
+        <v/>
+      </c>
+      <c r="Q46" s="13" t="n"/>
+    </row>
+    <row r="47" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>% profit / product sales</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11">
+        <f>IFERROR(D46/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E47" s="11">
+        <f>IFERROR(E46/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F47" s="11">
+        <f>IFERROR(F46/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IFERROR(G46/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H47" s="11">
+        <f>IFERROR(H46/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I47" s="11">
+        <f>IFERROR(I46/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J47" s="11">
+        <f>IFERROR(J46/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K47" s="11">
+        <f>IFERROR(K46/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L47" s="11">
+        <f>IFERROR(L46/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M47" s="11">
+        <f>IFERROR(M46/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N47" s="11">
+        <f>IFERROR(N46/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O47" s="11">
+        <f>IFERROR(O46/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P47" s="11">
+        <f>IFERROR(P46/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q47" s="11" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Stock final marcos</t>
-        </is>
-      </c>
       <c r="B48" s="4" t="n"/>
       <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n">
-        <v>13105.38</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>11635.01</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>10217.07</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>10174.5</v>
-      </c>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
@@ -3162,11 +3252,76 @@
       <c r="M48" s="4" t="n"/>
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
-      <c r="P48" s="4">
-        <f>SUM(D48:O48)</f>
-        <v/>
-      </c>
+      <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Stock inicial marcos</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n">
+        <v>15764.34</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>13105.38</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>11635.01</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>10232.85</v>
+      </c>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
+      <c r="P49" s="4">
+        <f>SUM(D49:O49)</f>
+        <v/>
+      </c>
+      <c r="Q49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>Stock final marcos</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n">
+        <v>13105.38</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>11635.01</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>10217.07</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>10174.5</v>
+      </c>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4">
+        <f>SUM(D50:O50)</f>
+        <v/>
+      </c>
+      <c r="Q50" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3176,19 +3331,19 @@
   <hyperlinks>
     <hyperlink ref="Q6" location="'i-shopify-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q7" location="'i-shopify-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q12" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q13" location="'g-expenses-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q17" location="'g-expenses-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q14" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q18" location="'g-expenses-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q20" location="'g-payment-fees-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q19" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q21" location="'g-payment-fees-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q31" location="'g-expenses-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q22" location="'g-payment-fees-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q32" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q33" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q34" location="'g-expenses-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q39" location="'g-expenses-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q40" location="'g-expenses-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q35" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q41" location="'g-expenses-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q42" location="'g-expenses-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q43" location="'g-expenses-inc'!A1" display="-&gt;"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3208,19 +3363,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -3268,7 +3423,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-03T06:03:31Z</t>
+          <t>2026-04-04T10:00:17Z</t>
         </is>
       </c>
     </row>
@@ -3302,59 +3457,59 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>line_item</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="J2" s="17" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -3394,7 +3549,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="17" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
@@ -3440,7 +3595,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="17" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
@@ -3486,7 +3641,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
@@ -3520,7 +3675,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1043.23</v>
+        <v>1645.88</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3532,11 +3687,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="17" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1043.23</v>
+        <v>1645.88</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3578,79 +3733,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>subcategory</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="J2" s="17" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="K2" s="17" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="M2" s="17" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>invoice_number</t>
         </is>
       </c>
-      <c r="N2" s="17" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
         <is>
           <t>drive_url</t>
         </is>
@@ -3700,7 +3855,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
@@ -3711,7 +3866,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>1220</t>
         </is>
@@ -3766,7 +3921,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
@@ -3777,7 +3932,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M4" s="19" t="inlineStr">
+      <c r="M4" s="18" t="inlineStr">
         <is>
           <t>2172-2199</t>
         </is>
@@ -3832,7 +3987,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
@@ -3843,7 +3998,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M5" s="19" t="inlineStr">
+      <c r="M5" s="18" t="inlineStr">
         <is>
           <t>34735793</t>
         </is>
@@ -3898,7 +4053,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
@@ -3909,7 +4064,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M6" s="19" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>34899776</t>
         </is>
@@ -3964,7 +4119,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
@@ -3975,7 +4130,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M7" s="19" t="inlineStr">
+      <c r="M7" s="18" t="inlineStr">
         <is>
           <t>35170891</t>
         </is>
@@ -4030,7 +4185,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
@@ -4041,7 +4196,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M8" s="19" t="inlineStr">
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t>35204899</t>
         </is>
@@ -4096,7 +4251,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
@@ -4107,7 +4262,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M9" s="19" t="inlineStr">
+      <c r="M9" s="18" t="inlineStr">
         <is>
           <t>AS-93451</t>
         </is>
@@ -4162,7 +4317,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
@@ -4173,7 +4328,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M10" s="19" t="inlineStr">
+      <c r="M10" s="18" t="inlineStr">
         <is>
           <t>AS-94908</t>
         </is>
@@ -4228,7 +4383,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
@@ -4239,7 +4394,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M11" s="19" t="inlineStr">
+      <c r="M11" s="18" t="inlineStr">
         <is>
           <t>AS-94969</t>
         </is>
@@ -4294,7 +4449,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J12" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
@@ -4305,7 +4460,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M12" s="19" t="inlineStr">
+      <c r="M12" s="18" t="inlineStr">
         <is>
           <t>AS-95058</t>
         </is>
@@ -4360,7 +4515,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
@@ -4371,7 +4526,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M13" s="19" t="inlineStr">
+      <c r="M13" s="18" t="inlineStr">
         <is>
           <t>AS-95513</t>
         </is>
@@ -4426,7 +4581,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J14" s="18" t="n">
+      <c r="J14" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
@@ -4437,7 +4592,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M14" s="19" t="inlineStr">
+      <c r="M14" s="18" t="inlineStr">
         <is>
           <t>AS-96265</t>
         </is>
@@ -4492,7 +4647,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
@@ -4503,7 +4658,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M15" s="19" t="inlineStr">
+      <c r="M15" s="18" t="inlineStr">
         <is>
           <t>AS-96361</t>
         </is>
@@ -4558,7 +4713,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J16" s="18" t="n">
+      <c r="J16" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
@@ -4569,7 +4724,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M16" s="19" t="inlineStr">
+      <c r="M16" s="18" t="inlineStr">
         <is>
           <t>10001458238017</t>
         </is>
@@ -4624,7 +4779,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J17" s="18" t="n">
+      <c r="J17" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
@@ -4635,7 +4790,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M17" s="19" t="inlineStr">
+      <c r="M17" s="18" t="inlineStr">
         <is>
           <t>3313-43306</t>
         </is>
@@ -4690,7 +4845,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J18" s="18" t="n">
+      <c r="J18" s="17" t="n">
         <v>1.1919</v>
       </c>
       <c r="K18" s="4" t="n">
@@ -4701,7 +4856,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M18" s="19" t="inlineStr">
+      <c r="M18" s="18" t="inlineStr">
         <is>
           <t>2026-0009</t>
         </is>
@@ -4756,7 +4911,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J19" s="18" t="n">
+      <c r="J19" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="4" t="n">
@@ -4767,7 +4922,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M19" s="19" t="inlineStr">
+      <c r="M19" s="18" t="inlineStr">
         <is>
           <t>171197</t>
         </is>
@@ -4822,7 +4977,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J20" s="18" t="n">
+      <c r="J20" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
@@ -4833,7 +4988,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M20" s="19" t="inlineStr">
+      <c r="M20" s="18" t="inlineStr">
         <is>
           <t>171198</t>
         </is>
@@ -4888,7 +5043,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J21" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="4" t="n">
@@ -4899,7 +5054,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M21" s="19" t="inlineStr">
+      <c r="M21" s="18" t="inlineStr">
         <is>
           <t>1236</t>
         </is>
@@ -4954,7 +5109,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J22" s="18" t="n">
+      <c r="J22" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="4" t="n">
@@ -4965,7 +5120,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M22" s="19" t="inlineStr">
+      <c r="M22" s="18" t="inlineStr">
         <is>
           <t>2353-3823</t>
         </is>
@@ -5020,7 +5175,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="J23" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="4" t="n">
@@ -5031,7 +5186,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M23" s="19" t="inlineStr">
+      <c r="M23" s="18" t="inlineStr">
         <is>
           <t>35389577</t>
         </is>
@@ -5086,7 +5241,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J24" s="18" t="n">
+      <c r="J24" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="4" t="n">
@@ -5097,7 +5252,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M24" s="19" t="inlineStr">
+      <c r="M24" s="18" t="inlineStr">
         <is>
           <t>35565709</t>
         </is>
@@ -5152,7 +5307,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J25" s="18" t="n">
+      <c r="J25" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="4" t="n">
@@ -5163,7 +5318,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M25" s="19" t="inlineStr">
+      <c r="M25" s="18" t="inlineStr">
         <is>
           <t>35722393</t>
         </is>
@@ -5218,7 +5373,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J26" s="18" t="n">
+      <c r="J26" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="4" t="n">
@@ -5229,7 +5384,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M26" s="19" t="inlineStr">
+      <c r="M26" s="18" t="inlineStr">
         <is>
           <t>35894810</t>
         </is>
@@ -5284,7 +5439,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J27" s="18" t="n">
+      <c r="J27" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="4" t="n">
@@ -5295,7 +5450,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M27" s="19" t="inlineStr">
+      <c r="M27" s="18" t="inlineStr">
         <is>
           <t>35920058</t>
         </is>
@@ -5350,7 +5505,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J28" s="18" t="n">
+      <c r="J28" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
@@ -5361,7 +5516,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M28" s="19" t="inlineStr">
+      <c r="M28" s="18" t="inlineStr">
         <is>
           <t>AS-97102</t>
         </is>
@@ -5416,7 +5571,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J29" s="18" t="n">
+      <c r="J29" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="n">
@@ -5427,7 +5582,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M29" s="19" t="inlineStr">
+      <c r="M29" s="18" t="inlineStr">
         <is>
           <t>AS-97313</t>
         </is>
@@ -5482,7 +5637,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J30" s="18" t="n">
+      <c r="J30" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="4" t="n">
@@ -5493,7 +5648,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M30" s="19" t="inlineStr">
+      <c r="M30" s="18" t="inlineStr">
         <is>
           <t>AS-97766</t>
         </is>
@@ -5548,7 +5703,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J31" s="18" t="n">
+      <c r="J31" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="n">
@@ -5559,7 +5714,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M31" s="19" t="inlineStr">
+      <c r="M31" s="18" t="inlineStr">
         <is>
           <t>AS-97929</t>
         </is>
@@ -5614,7 +5769,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J32" s="18" t="n">
+      <c r="J32" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="4" t="n">
@@ -5625,7 +5780,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M32" s="19" t="inlineStr">
+      <c r="M32" s="18" t="inlineStr">
         <is>
           <t>AS-98182</t>
         </is>
@@ -5680,7 +5835,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J33" s="18" t="n">
+      <c r="J33" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="4" t="n">
@@ -5691,7 +5846,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M33" s="19" t="inlineStr">
+      <c r="M33" s="18" t="inlineStr">
         <is>
           <t>AS-98184</t>
         </is>
@@ -5746,7 +5901,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J34" s="18" t="n">
+      <c r="J34" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="4" t="n">
@@ -5757,7 +5912,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M34" s="19" t="inlineStr">
+      <c r="M34" s="18" t="inlineStr">
         <is>
           <t>AS-98186</t>
         </is>
@@ -5812,7 +5967,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J35" s="18" t="n">
+      <c r="J35" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="4" t="n">
@@ -5823,7 +5978,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M35" s="19" t="inlineStr">
+      <c r="M35" s="18" t="inlineStr">
         <is>
           <t>AS-98295</t>
         </is>
@@ -5878,7 +6033,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J36" s="18" t="n">
+      <c r="J36" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="4" t="n">
@@ -5889,7 +6044,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M36" s="19" t="inlineStr">
+      <c r="M36" s="18" t="inlineStr">
         <is>
           <t>AS-98569</t>
         </is>
@@ -5944,7 +6099,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J37" s="18" t="n">
+      <c r="J37" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="4" t="n">
@@ -5955,7 +6110,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M37" s="19" t="inlineStr">
+      <c r="M37" s="18" t="inlineStr">
         <is>
           <t>AS-98850</t>
         </is>
@@ -6010,7 +6165,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J38" s="18" t="n">
+      <c r="J38" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="4" t="n">
@@ -6021,7 +6176,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M38" s="19" t="inlineStr">
+      <c r="M38" s="18" t="inlineStr">
         <is>
           <t>AS-99137</t>
         </is>
@@ -6076,7 +6231,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J39" s="18" t="n">
+      <c r="J39" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="4" t="n">
@@ -6087,7 +6242,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M39" s="19" t="inlineStr">
+      <c r="M39" s="18" t="inlineStr">
         <is>
           <t>AS-99148</t>
         </is>
@@ -6142,7 +6297,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J40" s="18" t="n">
+      <c r="J40" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="4" t="n">
@@ -6153,7 +6308,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M40" s="19" t="inlineStr">
+      <c r="M40" s="18" t="inlineStr">
         <is>
           <t>AS-99337</t>
         </is>
@@ -6208,7 +6363,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J41" s="18" t="n">
+      <c r="J41" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="4" t="n">
@@ -6219,7 +6374,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M41" s="19" t="inlineStr">
+      <c r="M41" s="18" t="inlineStr">
         <is>
           <t>AS-99436</t>
         </is>
@@ -6274,7 +6429,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J42" s="18" t="n">
+      <c r="J42" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="4" t="n">
@@ -6285,7 +6440,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M42" s="19" t="inlineStr">
+      <c r="M42" s="18" t="inlineStr">
         <is>
           <t>AS-99460</t>
         </is>
@@ -6340,7 +6495,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J43" s="18" t="n">
+      <c r="J43" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="4" t="n">
@@ -6351,7 +6506,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M43" s="19" t="inlineStr">
+      <c r="M43" s="18" t="inlineStr">
         <is>
           <t>AS-99461</t>
         </is>
@@ -6406,7 +6561,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J44" s="18" t="n">
+      <c r="J44" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="4" t="n">
@@ -6417,7 +6572,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M44" s="19" t="inlineStr">
+      <c r="M44" s="18" t="inlineStr">
         <is>
           <t>AS-99636</t>
         </is>
@@ -6472,7 +6627,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J45" s="18" t="n">
+      <c r="J45" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K45" s="4" t="n">
@@ -6483,7 +6638,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M45" s="19" t="inlineStr">
+      <c r="M45" s="18" t="inlineStr">
         <is>
           <t>AS-99795</t>
         </is>
@@ -6538,7 +6693,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J46" s="18" t="n">
+      <c r="J46" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K46" s="4" t="n">
@@ -6549,7 +6704,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M46" s="19" t="inlineStr">
+      <c r="M46" s="18" t="inlineStr">
         <is>
           <t>10001466838914</t>
         </is>
@@ -6604,7 +6759,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J47" s="18" t="n">
+      <c r="J47" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K47" s="4" t="n">
@@ -6615,7 +6770,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M47" s="19" t="inlineStr">
+      <c r="M47" s="18" t="inlineStr">
         <is>
           <t>3313-43718</t>
         </is>
@@ -6670,7 +6825,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J48" s="18" t="n">
+      <c r="J48" s="17" t="n">
         <v>1.1805</v>
       </c>
       <c r="K48" s="4" t="n">
@@ -6681,7 +6836,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M48" s="19" t="inlineStr">
+      <c r="M48" s="18" t="inlineStr">
         <is>
           <t>2026-0014</t>
         </is>
@@ -6736,7 +6891,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J49" s="18" t="n">
+      <c r="J49" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K49" s="4" t="n">
@@ -6747,7 +6902,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M49" s="19" t="inlineStr">
+      <c r="M49" s="18" t="inlineStr">
         <is>
           <t>171420</t>
         </is>
@@ -6802,7 +6957,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J50" s="18" t="n">
+      <c r="J50" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K50" s="4" t="n">
@@ -6813,7 +6968,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M50" s="19" t="inlineStr">
+      <c r="M50" s="18" t="inlineStr">
         <is>
           <t>171421</t>
         </is>
@@ -6868,7 +7023,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J51" s="18" t="n">
+      <c r="J51" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="4" t="n">
@@ -6879,7 +7034,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M51" s="19" t="inlineStr">
+      <c r="M51" s="18" t="inlineStr">
         <is>
           <t>1253</t>
         </is>
@@ -6934,7 +7089,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J52" s="18" t="n">
+      <c r="J52" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K52" s="4" t="n">
@@ -6945,7 +7100,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M52" s="19" t="inlineStr">
+      <c r="M52" s="18" t="inlineStr">
         <is>
           <t>6FF58AC</t>
         </is>
@@ -7000,7 +7155,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J53" s="18" t="n">
+      <c r="J53" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="4" t="n">
@@ -7011,7 +7166,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M53" s="19" t="inlineStr">
+      <c r="M53" s="18" t="inlineStr">
         <is>
           <t>2262-7837</t>
         </is>
@@ -7066,7 +7221,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J54" s="18" t="n">
+      <c r="J54" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="4" t="n">
@@ -7077,7 +7232,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M54" s="19" t="inlineStr">
+      <c r="M54" s="18" t="inlineStr">
         <is>
           <t>36093781</t>
         </is>
@@ -7132,7 +7287,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J55" s="18" t="n">
+      <c r="J55" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K55" s="4" t="n">
@@ -7143,7 +7298,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M55" s="19" t="inlineStr">
+      <c r="M55" s="18" t="inlineStr">
         <is>
           <t>36265975</t>
         </is>
@@ -7198,7 +7353,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J56" s="18" t="n">
+      <c r="J56" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="4" t="n">
@@ -7209,7 +7364,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M56" s="19" t="inlineStr">
+      <c r="M56" s="18" t="inlineStr">
         <is>
           <t>36427002</t>
         </is>
@@ -7264,7 +7419,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J57" s="18" t="n">
+      <c r="J57" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="4" t="n">
@@ -7275,7 +7430,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M57" s="19" t="inlineStr">
+      <c r="M57" s="18" t="inlineStr">
         <is>
           <t>36541238</t>
         </is>
@@ -7330,7 +7485,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J58" s="18" t="n">
+      <c r="J58" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="4" t="n">
@@ -7341,7 +7496,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M58" s="19" t="inlineStr">
+      <c r="M58" s="18" t="inlineStr">
         <is>
           <t>36584953</t>
         </is>
@@ -7396,7 +7551,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J59" s="18" t="n">
+      <c r="J59" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K59" s="4" t="n">
@@ -7407,7 +7562,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M59" s="19" t="inlineStr">
+      <c r="M59" s="18" t="inlineStr">
         <is>
           <t>36600953</t>
         </is>
@@ -7462,7 +7617,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J60" s="18" t="n">
+      <c r="J60" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K60" s="4" t="n">
@@ -7473,7 +7628,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M60" s="19" t="inlineStr">
+      <c r="M60" s="18" t="inlineStr">
         <is>
           <t>AS-100001</t>
         </is>
@@ -7528,7 +7683,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J61" s="18" t="n">
+      <c r="J61" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K61" s="4" t="n">
@@ -7539,7 +7694,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M61" s="19" t="inlineStr">
+      <c r="M61" s="18" t="inlineStr">
         <is>
           <t>AS-100189</t>
         </is>
@@ -7594,7 +7749,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J62" s="18" t="n">
+      <c r="J62" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="4" t="n">
@@ -7605,7 +7760,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M62" s="19" t="inlineStr">
+      <c r="M62" s="18" t="inlineStr">
         <is>
           <t>AS-100208</t>
         </is>
@@ -7660,7 +7815,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J63" s="18" t="n">
+      <c r="J63" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="4" t="n">
@@ -7671,7 +7826,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M63" s="19" t="inlineStr">
+      <c r="M63" s="18" t="inlineStr">
         <is>
           <t>AS-100505</t>
         </is>
@@ -7726,7 +7881,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J64" s="18" t="n">
+      <c r="J64" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="4" t="n">
@@ -7737,7 +7892,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M64" s="19" t="inlineStr">
+      <c r="M64" s="18" t="inlineStr">
         <is>
           <t>AS-100874</t>
         </is>
@@ -7792,7 +7947,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J65" s="18" t="n">
+      <c r="J65" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="4" t="n">
@@ -7803,7 +7958,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M65" s="19" t="inlineStr">
+      <c r="M65" s="18" t="inlineStr">
         <is>
           <t>AS-100996</t>
         </is>
@@ -7858,7 +8013,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J66" s="18" t="n">
+      <c r="J66" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K66" s="4" t="n">
@@ -7869,7 +8024,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M66" s="19" t="inlineStr">
+      <c r="M66" s="18" t="inlineStr">
         <is>
           <t>AS-101113</t>
         </is>
@@ -7924,7 +8079,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J67" s="18" t="n">
+      <c r="J67" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K67" s="4" t="n">
@@ -7935,7 +8090,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M67" s="19" t="inlineStr">
+      <c r="M67" s="18" t="inlineStr">
         <is>
           <t>AS-101200</t>
         </is>
@@ -7990,7 +8145,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J68" s="18" t="n">
+      <c r="J68" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K68" s="4" t="n">
@@ -8001,7 +8156,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M68" s="19" t="inlineStr">
+      <c r="M68" s="18" t="inlineStr">
         <is>
           <t>AS-101203</t>
         </is>
@@ -8056,7 +8211,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J69" s="18" t="n">
+      <c r="J69" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="4" t="n">
@@ -8067,7 +8222,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M69" s="19" t="inlineStr">
+      <c r="M69" s="18" t="inlineStr">
         <is>
           <t>AS-101378</t>
         </is>
@@ -8122,7 +8277,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J70" s="18" t="n">
+      <c r="J70" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="4" t="n">
@@ -8133,7 +8288,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M70" s="19" t="inlineStr">
+      <c r="M70" s="18" t="inlineStr">
         <is>
           <t>AS-101565</t>
         </is>
@@ -8188,7 +8343,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J71" s="18" t="n">
+      <c r="J71" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K71" s="4" t="n">
@@ -8199,7 +8354,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M71" s="19" t="inlineStr">
+      <c r="M71" s="18" t="inlineStr">
         <is>
           <t>AS-101625</t>
         </is>
@@ -8254,7 +8409,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J72" s="18" t="n">
+      <c r="J72" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K72" s="4" t="n">
@@ -8265,7 +8420,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M72" s="19" t="inlineStr">
+      <c r="M72" s="18" t="inlineStr">
         <is>
           <t>AS-101687</t>
         </is>
@@ -8320,7 +8475,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J73" s="18" t="n">
+      <c r="J73" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K73" s="4" t="n">
@@ -8331,7 +8486,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M73" s="19" t="inlineStr">
+      <c r="M73" s="18" t="inlineStr">
         <is>
           <t>AS-101720</t>
         </is>
@@ -8386,7 +8541,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J74" s="18" t="n">
+      <c r="J74" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K74" s="4" t="n">
@@ -8397,7 +8552,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M74" s="19" t="inlineStr">
+      <c r="M74" s="18" t="inlineStr">
         <is>
           <t>AS-101875</t>
         </is>
@@ -8452,7 +8607,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J75" s="18" t="n">
+      <c r="J75" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K75" s="4" t="n">
@@ -8463,7 +8618,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M75" s="19" t="inlineStr">
+      <c r="M75" s="18" t="inlineStr">
         <is>
           <t>AS-101899</t>
         </is>
@@ -8518,7 +8673,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J76" s="18" t="n">
+      <c r="J76" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K76" s="4" t="n">
@@ -8529,7 +8684,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M76" s="19" t="inlineStr">
+      <c r="M76" s="18" t="inlineStr">
         <is>
           <t>AS-101925</t>
         </is>
@@ -8584,7 +8739,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J77" s="18" t="n">
+      <c r="J77" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K77" s="4" t="n">
@@ -8595,7 +8750,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M77" s="19" t="inlineStr">
+      <c r="M77" s="18" t="inlineStr">
         <is>
           <t>AS-101927</t>
         </is>
@@ -8650,7 +8805,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J78" s="18" t="n">
+      <c r="J78" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K78" s="4" t="n">
@@ -8661,7 +8816,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M78" s="19" t="inlineStr">
+      <c r="M78" s="18" t="inlineStr">
         <is>
           <t>AS-101932</t>
         </is>
@@ -8716,7 +8871,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J79" s="18" t="n">
+      <c r="J79" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K79" s="4" t="n">
@@ -8727,7 +8882,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M79" s="19" t="inlineStr">
+      <c r="M79" s="18" t="inlineStr">
         <is>
           <t>AS-102156</t>
         </is>
@@ -8782,7 +8937,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J80" s="18" t="n">
+      <c r="J80" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K80" s="4" t="n">
@@ -8793,7 +8948,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M80" s="19" t="inlineStr">
+      <c r="M80" s="18" t="inlineStr">
         <is>
           <t>AS-102233</t>
         </is>
@@ -8848,7 +9003,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J81" s="18" t="n">
+      <c r="J81" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
@@ -8859,7 +9014,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M81" s="19" t="inlineStr">
+      <c r="M81" s="18" t="inlineStr">
         <is>
           <t>AS-99872</t>
         </is>
@@ -8914,7 +9069,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J82" s="18" t="n">
+      <c r="J82" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K82" s="4" t="n">
@@ -8925,7 +9080,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M82" s="19" t="inlineStr">
+      <c r="M82" s="18" t="inlineStr">
         <is>
           <t>10001475281494</t>
         </is>
@@ -8980,7 +9135,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J83" s="18" t="n">
+      <c r="J83" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K83" s="4" t="n">
@@ -8991,7 +9146,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M83" s="19" t="inlineStr">
+      <c r="M83" s="18" t="inlineStr">
         <is>
           <t>1268</t>
         </is>
@@ -9112,54 +9267,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -9194,7 +9349,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="4" t="n">
@@ -9235,7 +9390,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
@@ -9276,7 +9431,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
@@ -9305,7 +9460,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>30.7</v>
+        <v>43.42</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -9317,11 +9472,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>30.7</v>
+        <v>43.42</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -9356,44 +9511,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>rate_date</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>reference_rate</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -9420,10 +9575,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E3" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="18" t="n">
+      <c r="E3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="17" t="n">
         <v>1.1919</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -9453,10 +9608,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E4" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="18" t="n">
+      <c r="E4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -9486,10 +9641,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="18" t="n">
+      <c r="E5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="17" t="n">
         <v>1.1805</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -9519,10 +9674,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="18" t="n">
+      <c r="E6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -9552,10 +9707,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="18" t="n">
+      <c r="E7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -9585,10 +9740,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E8" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="18" t="n">
+      <c r="E8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -9622,34 +9777,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>current_folder</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>destination_path</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -9892,7 +10047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9984,7 +10139,7 @@
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>Nº Facturas INC 2026</t>
         </is>
@@ -10058,151 +10213,151 @@
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Turnover</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n"/>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="22" t="n">
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" s="22" t="n"/>
+      <c r="Q4" s="21" t="n"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="A5" s="23" t="n"/>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="A5" s="22" t="n"/>
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Product sales</t>
         </is>
       </c>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="23" t="n">
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="Q5" s="23" t="n"/>
+      <c r="Q5" s="22" t="n"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="A6" s="25" t="n"/>
-      <c r="B6" s="25" t="n"/>
+      <c r="A6" s="24" t="n"/>
+      <c r="B6" s="24" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="25" t="n">
+      <c r="D6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" s="25" t="n"/>
+      <c r="Q6" s="24" t="n"/>
     </row>
     <row r="7" ht="12" customHeight="1">
       <c r="C7" t="inlineStr">
@@ -10251,728 +10406,731 @@
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="A8" s="25" t="n"/>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Otros ingresos</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="n"/>
-      <c r="D8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="25" t="n"/>
-    </row>
-    <row r="9" ht="12" customHeight="1"/>
-    <row r="10" ht="12" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A8" s="22" t="n"/>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="22" t="n"/>
+    </row>
+    <row r="9" ht="12" customHeight="1">
+      <c r="A9" s="24" t="n"/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Uncategorized income</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="12" customHeight="1"/>
+    <row r="11" ht="12" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n">
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E11" s="21" t="n">
         <v>31</v>
       </c>
-      <c r="F10" s="22" t="n">
-        <v>32</v>
-      </c>
-      <c r="G10" s="22" t="n">
+      <c r="F11" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="G11" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="22" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q10" s="22" t="n"/>
-    </row>
-    <row r="11" ht="12" customHeight="1">
-      <c r="A11" s="23" t="n"/>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="H11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q11" s="21" t="n"/>
+    </row>
+    <row r="12" ht="12" customHeight="1">
+      <c r="A12" s="22" t="n"/>
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n">
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E12" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F12" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="G11" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="23" t="n">
+      <c r="G12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="Q11" s="23" t="n"/>
-    </row>
-    <row r="12" ht="12" customHeight="1">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="Q12" s="22" t="n"/>
+    </row>
+    <row r="13" ht="12" customHeight="1">
+      <c r="A13" s="24" t="n"/>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E13" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F13" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="G12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="25" t="n">
+      <c r="G13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="24" t="n">
         <v>49</v>
       </c>
-      <c r="Q12" s="25" t="n"/>
-    </row>
-    <row r="13" ht="12" customHeight="1">
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>JONDO</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F13" t="n">
-        <v>22</v>
-      </c>
-      <c r="G13" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>47</v>
-      </c>
+      <c r="Q13" s="24" t="n"/>
     </row>
     <row r="14" ht="12" customHeight="1">
       <c r="C14" t="inlineStr">
         <is>
+          <t>JONDO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" ht="12" customHeight="1">
+      <c r="C15" t="inlineStr">
+        <is>
           <t>TGI</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="15" ht="12" customHeight="1">
-      <c r="A15" s="25" t="n"/>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="9" t="inlineStr">
+    <row r="16" ht="12" customHeight="1">
+      <c r="A16" s="24" t="n"/>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Logistics</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="25" t="n">
+      <c r="D16" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" s="25" t="n"/>
-    </row>
-    <row r="16" ht="12" customHeight="1">
-      <c r="C16" t="inlineStr">
+      <c r="Q16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="12" customHeight="1">
+      <c r="C17" t="inlineStr">
         <is>
           <t>TGI</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="17" ht="12" customHeight="1">
-      <c r="A17" s="25" t="n"/>
-      <c r="B17" s="25" t="n"/>
-      <c r="C17" s="9" t="inlineStr">
+    <row r="18" ht="12" customHeight="1">
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Payment fees</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="25" t="n">
+      <c r="D18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="Q17" s="25" t="n"/>
-    </row>
-    <row r="18" ht="12" customHeight="1">
-      <c r="C18" t="inlineStr">
+      <c r="Q18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="12" customHeight="1">
+      <c r="C19" t="inlineStr">
         <is>
           <t>SHOPIFY</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="19" ht="12" customHeight="1"/>
-    <row r="20" ht="12" customHeight="1">
-      <c r="A20" s="23" t="n"/>
-      <c r="B20" s="24" t="inlineStr">
+    <row r="20" ht="12" customHeight="1"/>
+    <row r="21" ht="12" customHeight="1">
+      <c r="A21" s="22" t="n"/>
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Opex</t>
         </is>
       </c>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n">
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E21" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="F20" s="23" t="n">
+      <c r="F21" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q21" s="22" t="n"/>
+    </row>
+    <row r="22" ht="12" customHeight="1">
+      <c r="A22" s="24" t="n"/>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Shared services</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="12" customHeight="1">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SHAREDSERVICESSL</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" ht="12" customHeight="1">
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="G20" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q20" s="23" t="n"/>
-    </row>
-    <row r="21" ht="12" customHeight="1">
-      <c r="A21" s="25" t="n"/>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Shared services</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" s="25" t="n"/>
-    </row>
-    <row r="22" ht="12" customHeight="1">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SHAREDSERVICESSL</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" ht="12" customHeight="1">
-      <c r="A23" s="25" t="n"/>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F23" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="G23" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="25" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q23" s="25" t="n"/>
-    </row>
-    <row r="24" ht="12" customHeight="1">
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CONTINUUM</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>4</v>
-      </c>
+      <c r="F24" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q24" s="24" t="n"/>
     </row>
     <row r="25" ht="12" customHeight="1">
       <c r="C25" t="inlineStr">
         <is>
-          <t>HUSHED</t>
+          <t>CONTINUUM</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -10984,8 +11142,8 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="26" t="n">
-        <v>0</v>
+      <c r="G25" t="n">
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -11012,25 +11170,25 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" ht="12" customHeight="1">
       <c r="C26" t="inlineStr">
         <is>
-          <t>IPOSTAL</t>
+          <t>DELAWARE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
-      </c>
-      <c r="G26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
@@ -11058,13 +11216,13 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" ht="12" customHeight="1">
       <c r="C27" t="inlineStr">
         <is>
-          <t>QUICKBOOKS</t>
+          <t>HUSHED</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -11076,7 +11234,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="26" t="n">
+      <c r="G27" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
@@ -11110,19 +11268,19 @@
     <row r="28" ht="12" customHeight="1">
       <c r="C28" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>IPOSTAL</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G28" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
@@ -11150,201 +11308,293 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="A29" s="25" t="n"/>
-      <c r="B29" s="25" t="n"/>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="25" t="n">
-        <v>0</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>QUICKBOOKS</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
       </c>
       <c r="G29" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="25" t="n"/>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" ht="12" customHeight="1">
       <c r="C30" t="inlineStr">
         <is>
+          <t>REGUS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" ht="12" customHeight="1">
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="24" t="n"/>
+    </row>
+    <row r="32" ht="12" customHeight="1">
+      <c r="C32" t="inlineStr">
+        <is>
           <t>REVER</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="12" customHeight="1">
-      <c r="A31" s="25" t="n"/>
-      <c r="B31" s="25" t="n"/>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Otros gastos</t>
-        </is>
-      </c>
-      <c r="D31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="25" t="n"/>
-    </row>
-    <row r="32" ht="12" customHeight="1">
-      <c r="A32" s="25" t="n"/>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>Diferencias divisas</t>
-        </is>
-      </c>
-      <c r="C32" s="25" t="n"/>
-      <c r="D32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="25" t="n"/>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="12" customHeight="1">
+      <c r="A33" s="24" t="n"/>
+      <c r="B33" s="24" t="n"/>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Uncategorized Expenses</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="24" t="n"/>
+    </row>
+    <row r="34" ht="12" customHeight="1">
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/output/spreadsheet/pyg_inc_2026.xlsx
+++ b/output/spreadsheet/pyg_inc_2026.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="165" formatCode="0.00000000"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);-"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
     </font>
     <font>
       <b val="1"/>
@@ -124,9 +127,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -143,15 +146,16 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -527,7 +531,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -698,7 +702,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Actualizado: 04/04/2026 12:00 h</t>
+          <t>Actualizado: 10/04/2026 11:48 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1128,51 +1132,51 @@
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6">
-        <f>D12+D31</f>
+        <f>D12+D32</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>E12+E31</f>
+        <f>E12+E32</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>F12+F31</f>
+        <f>F12+F32</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>G12+G31</f>
+        <f>G12+G32</f>
         <v/>
       </c>
       <c r="H11" s="6">
-        <f>H12+H31</f>
+        <f>H12+H32</f>
         <v/>
       </c>
       <c r="I11" s="6">
-        <f>I12+I31</f>
+        <f>I12+I32</f>
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>J12+J31</f>
+        <f>J12+J32</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>K12+K31</f>
+        <f>K12+K32</f>
         <v/>
       </c>
       <c r="L11" s="6">
-        <f>L12+L31</f>
+        <f>L12+L32</f>
         <v/>
       </c>
       <c r="M11" s="6">
-        <f>M12+M31</f>
+        <f>M12+M32</f>
         <v/>
       </c>
       <c r="N11" s="6">
-        <f>N12+N31</f>
+        <f>N12+N32</f>
         <v/>
       </c>
       <c r="O11" s="6">
-        <f>O12+O31</f>
+        <f>O12+O32</f>
         <v/>
       </c>
       <c r="P11" s="6">
@@ -1455,7 +1459,7 @@
         <v>1496.84</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>58.35</v>
+        <v>67.3</v>
       </c>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n"/>
@@ -1860,11 +1864,22 @@
       </c>
     </row>
     <row r="23" ht="12" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Royalties</t>
+        </is>
+      </c>
       <c r="B23" s="4" t="n"/>
       <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
+      <c r="D23" s="4" t="n">
+        <v>561.38</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>878.29</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>852</v>
+      </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
@@ -1880,679 +1895,634 @@
       </c>
       <c r="Q23" s="4" t="n"/>
     </row>
-    <row r="24" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="24" ht="12" customHeight="1">
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4">
+        <f>SUM(D24:O24)</f>
+        <v/>
+      </c>
+      <c r="Q24" s="4" t="n"/>
+    </row>
+    <row r="25" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % Payment fees / sales</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11">
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11">
         <f>IFERROR(D21/D5,0)</f>
         <v/>
       </c>
-      <c r="E24" s="11">
+      <c r="E25" s="11">
         <f>IFERROR(E21/E5,0)</f>
         <v/>
       </c>
-      <c r="F24" s="11">
+      <c r="F25" s="11">
         <f>IFERROR(F21/F5,0)</f>
         <v/>
       </c>
-      <c r="G24" s="11">
+      <c r="G25" s="11">
         <f>IFERROR(G21/G5,0)</f>
         <v/>
       </c>
-      <c r="H24" s="11">
+      <c r="H25" s="11">
         <f>IFERROR(H21/H5,0)</f>
         <v/>
       </c>
-      <c r="I24" s="11">
+      <c r="I25" s="11">
         <f>IFERROR(I21/I5,0)</f>
         <v/>
       </c>
-      <c r="J24" s="11">
+      <c r="J25" s="11">
         <f>IFERROR(J21/J5,0)</f>
         <v/>
       </c>
-      <c r="K24" s="11">
+      <c r="K25" s="11">
         <f>IFERROR(K21/K5,0)</f>
         <v/>
       </c>
-      <c r="L24" s="11">
+      <c r="L25" s="11">
         <f>IFERROR(L21/L5,0)</f>
         <v/>
       </c>
-      <c r="M24" s="11">
+      <c r="M25" s="11">
         <f>IFERROR(M21/M5,0)</f>
         <v/>
       </c>
-      <c r="N24" s="11">
+      <c r="N25" s="11">
         <f>IFERROR(N21/N5,0)</f>
         <v/>
       </c>
-      <c r="O24" s="11">
+      <c r="O25" s="11">
         <f>IFERROR(O21/O5,0)</f>
         <v/>
       </c>
-      <c r="P24" s="11">
+      <c r="P25" s="11">
         <f>IFERROR(P21/P5,0)</f>
         <v/>
       </c>
-      <c r="Q24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
-      <c r="O25" s="4" t="n"/>
-      <c r="P25" s="4">
-        <f>SUM(D25:O25)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="4" t="n"/>
+      <c r="Q25" s="11" t="n"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4">
+        <f>SUM(D26:O26)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="12" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>GROSS MARGIN (SALES-MANUFACTURING)</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13">
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14">
         <f>D5-D13</f>
         <v/>
       </c>
-      <c r="E26" s="13">
+      <c r="E27" s="14">
         <f>E5-E13</f>
         <v/>
       </c>
-      <c r="F26" s="13">
+      <c r="F27" s="14">
         <f>F5-F13</f>
         <v/>
       </c>
-      <c r="G26" s="13">
+      <c r="G27" s="14">
         <f>G5-G13</f>
         <v/>
       </c>
-      <c r="H26" s="13">
+      <c r="H27" s="14">
         <f>H5-H13</f>
         <v/>
       </c>
-      <c r="I26" s="13">
+      <c r="I27" s="14">
         <f>I5-I13</f>
         <v/>
       </c>
-      <c r="J26" s="13">
+      <c r="J27" s="14">
         <f>J5-J13</f>
         <v/>
       </c>
-      <c r="K26" s="13">
+      <c r="K27" s="14">
         <f>K5-K13</f>
         <v/>
       </c>
-      <c r="L26" s="13">
+      <c r="L27" s="14">
         <f>L5-L13</f>
         <v/>
       </c>
-      <c r="M26" s="13">
+      <c r="M27" s="14">
         <f>M5-M13</f>
         <v/>
       </c>
-      <c r="N26" s="13">
+      <c r="N27" s="14">
         <f>N5-N13</f>
         <v/>
       </c>
-      <c r="O26" s="13">
+      <c r="O27" s="14">
         <f>O5-O13</f>
         <v/>
       </c>
-      <c r="P26" s="13">
-        <f>SUM(D26:O26)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="13" t="n"/>
-    </row>
-    <row r="27" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="P27" s="14">
+        <f>SUM(D27:O27)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="14" t="n"/>
+    </row>
+    <row r="28" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>% gross margin</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11">
-        <f>IFERROR(D26/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E27" s="11">
-        <f>IFERROR(E26/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F27" s="11">
-        <f>IFERROR(F26/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G27" s="11">
-        <f>IFERROR(G26/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H27" s="11">
-        <f>IFERROR(H26/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I27" s="11">
-        <f>IFERROR(I26/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J27" s="11">
-        <f>IFERROR(J26/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K27" s="11">
-        <f>IFERROR(K26/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L27" s="11">
-        <f>IFERROR(L26/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M27" s="11">
-        <f>IFERROR(M26/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N27" s="11">
-        <f>IFERROR(N26/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O27" s="11">
-        <f>IFERROR(O26/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P27" s="11">
-        <f>IFERROR(P26/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="11" t="n"/>
-    </row>
-    <row r="28" ht="12" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11">
+        <f>IFERROR(D27/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E28" s="11">
+        <f>IFERROR(E27/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F28" s="11">
+        <f>IFERROR(F27/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="11">
+        <f>IFERROR(G27/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="11">
+        <f>IFERROR(H27/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I28" s="11">
+        <f>IFERROR(I27/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J28" s="11">
+        <f>IFERROR(J27/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="11">
+        <f>IFERROR(K27/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L28" s="11">
+        <f>IFERROR(L27/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M28" s="11">
+        <f>IFERROR(M27/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N28" s="11">
+        <f>IFERROR(N27/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O28" s="11">
+        <f>IFERROR(O27/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P28" s="11">
+        <f>IFERROR(P27/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="12" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Contributive margin (product sales-COGS)</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13">
-        <f>D5-D12</f>
-        <v/>
-      </c>
-      <c r="E28" s="13">
-        <f>E5-E12</f>
-        <v/>
-      </c>
-      <c r="F28" s="13">
-        <f>F5-F12</f>
-        <v/>
-      </c>
-      <c r="G28" s="13">
-        <f>G5-G12</f>
-        <v/>
-      </c>
-      <c r="H28" s="13">
-        <f>H5-H12</f>
-        <v/>
-      </c>
-      <c r="I28" s="13">
-        <f>I5-I12</f>
-        <v/>
-      </c>
-      <c r="J28" s="13">
-        <f>J5-J12</f>
-        <v/>
-      </c>
-      <c r="K28" s="13">
-        <f>K5-K12</f>
-        <v/>
-      </c>
-      <c r="L28" s="13">
-        <f>L5-L12</f>
-        <v/>
-      </c>
-      <c r="M28" s="13">
-        <f>M5-M12</f>
-        <v/>
-      </c>
-      <c r="N28" s="13">
-        <f>N5-N12</f>
-        <v/>
-      </c>
-      <c r="O28" s="13">
-        <f>O5-O12</f>
-        <v/>
-      </c>
-      <c r="P28" s="13">
-        <f>SUM(D28:O28)</f>
-        <v/>
-      </c>
-      <c r="Q28" s="13" t="n"/>
-    </row>
-    <row r="29" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14">
+        <f>D5-D12-D23</f>
+        <v/>
+      </c>
+      <c r="E29" s="14">
+        <f>E5-E12-E23</f>
+        <v/>
+      </c>
+      <c r="F29" s="14">
+        <f>F5-F12-F23</f>
+        <v/>
+      </c>
+      <c r="G29" s="14">
+        <f>G5-G12-G23</f>
+        <v/>
+      </c>
+      <c r="H29" s="14">
+        <f>H5-H12-H23</f>
+        <v/>
+      </c>
+      <c r="I29" s="14">
+        <f>I5-I12-I23</f>
+        <v/>
+      </c>
+      <c r="J29" s="14">
+        <f>J5-J12-J23</f>
+        <v/>
+      </c>
+      <c r="K29" s="14">
+        <f>K5-K12-K23</f>
+        <v/>
+      </c>
+      <c r="L29" s="14">
+        <f>L5-L12-L23</f>
+        <v/>
+      </c>
+      <c r="M29" s="14">
+        <f>M5-M12-M23</f>
+        <v/>
+      </c>
+      <c r="N29" s="14">
+        <f>N5-N12-N23</f>
+        <v/>
+      </c>
+      <c r="O29" s="14">
+        <f>O5-O12-O23</f>
+        <v/>
+      </c>
+      <c r="P29" s="14">
+        <f>SUM(D29:O29)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="14" t="n"/>
+    </row>
+    <row r="30" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>% contributive margin</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11">
-        <f>IFERROR(D28/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E29" s="11">
-        <f>IFERROR(E28/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F29" s="11">
-        <f>IFERROR(F28/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G29" s="11">
-        <f>IFERROR(G28/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H29" s="11">
-        <f>IFERROR(H28/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I29" s="11">
-        <f>IFERROR(I28/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J29" s="11">
-        <f>IFERROR(J28/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K29" s="11">
-        <f>IFERROR(K28/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L29" s="11">
-        <f>IFERROR(L28/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M29" s="11">
-        <f>IFERROR(M28/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N29" s="11">
-        <f>IFERROR(N28/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O29" s="11">
-        <f>IFERROR(O28/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P29" s="11">
-        <f>IFERROR(P28/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="11" t="n"/>
-    </row>
-    <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4">
-        <f>SUM(D30:O30)</f>
-        <v/>
-      </c>
-      <c r="Q30" s="4" t="n"/>
-    </row>
-    <row r="31" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11">
+        <f>IFERROR(D29/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E30" s="11">
+        <f>IFERROR(E29/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="11">
+        <f>IFERROR(F29/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IFERROR(G29/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="11">
+        <f>IFERROR(H29/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I30" s="11">
+        <f>IFERROR(I29/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J30" s="11">
+        <f>IFERROR(J29/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="11">
+        <f>IFERROR(K29/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="11">
+        <f>IFERROR(L29/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M30" s="11">
+        <f>IFERROR(M29/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N30" s="11">
+        <f>IFERROR(N29/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O30" s="11">
+        <f>IFERROR(O29/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P30" s="11">
+        <f>IFERROR(P29/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="12" customHeight="1">
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4">
+        <f>SUM(D31:O31)</f>
+        <v/>
+      </c>
+      <c r="Q31" s="4" t="n"/>
+    </row>
+    <row r="32" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Opex</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8">
-        <f>D32+D34+D41+D43</f>
-        <v/>
-      </c>
-      <c r="E31" s="8">
-        <f>E32+E34+E41+E43</f>
-        <v/>
-      </c>
-      <c r="F31" s="8">
-        <f>F32+F34+F41+F43</f>
-        <v/>
-      </c>
-      <c r="G31" s="8">
-        <f>G32+G34+G41+G43</f>
-        <v/>
-      </c>
-      <c r="H31" s="8">
-        <f>H32+H34+H41+H43</f>
-        <v/>
-      </c>
-      <c r="I31" s="8">
-        <f>I32+I34+I41+I43</f>
-        <v/>
-      </c>
-      <c r="J31" s="8">
-        <f>J32+J34+J41+J43</f>
-        <v/>
-      </c>
-      <c r="K31" s="8">
-        <f>K32+K34+K41+K43</f>
-        <v/>
-      </c>
-      <c r="L31" s="8">
-        <f>L32+L34+L41+L43</f>
-        <v/>
-      </c>
-      <c r="M31" s="8">
-        <f>M32+M34+M41+M43</f>
-        <v/>
-      </c>
-      <c r="N31" s="8">
-        <f>N32+N34+N41+N43</f>
-        <v/>
-      </c>
-      <c r="O31" s="8">
-        <f>O32+O34+O41+O43</f>
-        <v/>
-      </c>
-      <c r="P31" s="8">
-        <f>SUM(D31:O31)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="8" t="n"/>
-    </row>
-    <row r="32" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8">
+        <f>D33+D35+D42+D44</f>
+        <v/>
+      </c>
+      <c r="E32" s="8">
+        <f>E33+E35+E42+E44</f>
+        <v/>
+      </c>
+      <c r="F32" s="8">
+        <f>F33+F35+F42+F44</f>
+        <v/>
+      </c>
+      <c r="G32" s="8">
+        <f>G33+G35+G42+G44</f>
+        <v/>
+      </c>
+      <c r="H32" s="8">
+        <f>H33+H35+H42+H44</f>
+        <v/>
+      </c>
+      <c r="I32" s="8">
+        <f>I33+I35+I42+I44</f>
+        <v/>
+      </c>
+      <c r="J32" s="8">
+        <f>J33+J35+J42+J44</f>
+        <v/>
+      </c>
+      <c r="K32" s="8">
+        <f>K33+K35+K42+K44</f>
+        <v/>
+      </c>
+      <c r="L32" s="8">
+        <f>L33+L35+L42+L44</f>
+        <v/>
+      </c>
+      <c r="M32" s="8">
+        <f>M33+M35+M42+M44</f>
+        <v/>
+      </c>
+      <c r="N32" s="8">
+        <f>N33+N35+N42+N44</f>
+        <v/>
+      </c>
+      <c r="O32" s="8">
+        <f>O33+O35+O42+O44</f>
+        <v/>
+      </c>
+      <c r="P32" s="8">
+        <f>SUM(D32:O32)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="8" t="n"/>
+    </row>
+    <row r="33" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Shared services</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10">
-        <f>SUM(D33:D33)</f>
-        <v/>
-      </c>
-      <c r="E32" s="10">
-        <f>SUM(E33:E33)</f>
-        <v/>
-      </c>
-      <c r="F32" s="10">
-        <f>SUM(F33:F33)</f>
-        <v/>
-      </c>
-      <c r="G32" s="10">
-        <f>SUM(G33:G33)</f>
-        <v/>
-      </c>
-      <c r="H32" s="10">
-        <f>SUM(H33:H33)</f>
-        <v/>
-      </c>
-      <c r="I32" s="10">
-        <f>SUM(I33:I33)</f>
-        <v/>
-      </c>
-      <c r="J32" s="10">
-        <f>SUM(J33:J33)</f>
-        <v/>
-      </c>
-      <c r="K32" s="10">
-        <f>SUM(K33:K33)</f>
-        <v/>
-      </c>
-      <c r="L32" s="10">
-        <f>SUM(L33:L33)</f>
-        <v/>
-      </c>
-      <c r="M32" s="10">
-        <f>SUM(M33:M33)</f>
-        <v/>
-      </c>
-      <c r="N32" s="10">
-        <f>SUM(N33:N33)</f>
-        <v/>
-      </c>
-      <c r="O32" s="10">
-        <f>SUM(O33:O33)</f>
-        <v/>
-      </c>
-      <c r="P32" s="10">
-        <f>SUM(D32:O32)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="10" t="inlineStr">
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10">
+        <f>SUM(D34:D34)</f>
+        <v/>
+      </c>
+      <c r="E33" s="10">
+        <f>SUM(E34:E34)</f>
+        <v/>
+      </c>
+      <c r="F33" s="10">
+        <f>SUM(F34:F34)</f>
+        <v/>
+      </c>
+      <c r="G33" s="10">
+        <f>SUM(G34:G34)</f>
+        <v/>
+      </c>
+      <c r="H33" s="10">
+        <f>SUM(H34:H34)</f>
+        <v/>
+      </c>
+      <c r="I33" s="10">
+        <f>SUM(I34:I34)</f>
+        <v/>
+      </c>
+      <c r="J33" s="10">
+        <f>SUM(J34:J34)</f>
+        <v/>
+      </c>
+      <c r="K33" s="10">
+        <f>SUM(K34:K34)</f>
+        <v/>
+      </c>
+      <c r="L33" s="10">
+        <f>SUM(L34:L34)</f>
+        <v/>
+      </c>
+      <c r="M33" s="10">
+        <f>SUM(M34:M34)</f>
+        <v/>
+      </c>
+      <c r="N33" s="10">
+        <f>SUM(N34:N34)</f>
+        <v/>
+      </c>
+      <c r="O33" s="10">
+        <f>SUM(O34:O34)</f>
+        <v/>
+      </c>
+      <c r="P33" s="10">
+        <f>SUM(D33:O33)</f>
+        <v/>
+      </c>
+      <c r="Q33" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="33" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t xml:space="preserve">      SHAREDSERVICESSL</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="E33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="F33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="G33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="H33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="I33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="J33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="K33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="L33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="M33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="N33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="O33" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A33))</f>
-        <v/>
-      </c>
-      <c r="P33" s="4">
-        <f>SUM(D33:O33)</f>
-        <v/>
-      </c>
-      <c r="Q33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="E34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="F34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="G34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="H34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="I34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="J34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="K34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="L34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="M34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="N34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="O34" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
+        <v/>
+      </c>
+      <c r="P34" s="4">
+        <f>SUM(D34:O34)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="34" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="35" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Administration</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10">
-        <f>SUM(D35:D40)</f>
-        <v/>
-      </c>
-      <c r="E34" s="10">
-        <f>SUM(E35:E40)</f>
-        <v/>
-      </c>
-      <c r="F34" s="10">
-        <f>SUM(F35:F40)</f>
-        <v/>
-      </c>
-      <c r="G34" s="10">
-        <f>SUM(G35:G40)</f>
-        <v/>
-      </c>
-      <c r="H34" s="10">
-        <f>SUM(H35:H40)</f>
-        <v/>
-      </c>
-      <c r="I34" s="10">
-        <f>SUM(I35:I40)</f>
-        <v/>
-      </c>
-      <c r="J34" s="10">
-        <f>SUM(J35:J40)</f>
-        <v/>
-      </c>
-      <c r="K34" s="10">
-        <f>SUM(K35:K40)</f>
-        <v/>
-      </c>
-      <c r="L34" s="10">
-        <f>SUM(L35:L40)</f>
-        <v/>
-      </c>
-      <c r="M34" s="10">
-        <f>SUM(M35:M40)</f>
-        <v/>
-      </c>
-      <c r="N34" s="10">
-        <f>SUM(N35:N40)</f>
-        <v/>
-      </c>
-      <c r="O34" s="10">
-        <f>SUM(O35:O40)</f>
-        <v/>
-      </c>
-      <c r="P34" s="10">
-        <f>SUM(D34:O34)</f>
-        <v/>
-      </c>
-      <c r="Q34" s="10" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      CONTINUUM</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="E35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="F35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="G35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="H35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="I35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="J35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="K35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="L35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="M35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="N35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="O35" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="P35" s="4">
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10">
+        <f>SUM(D36:D41)</f>
+        <v/>
+      </c>
+      <c r="E35" s="10">
+        <f>SUM(E36:E41)</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>SUM(F36:F41)</f>
+        <v/>
+      </c>
+      <c r="G35" s="10">
+        <f>SUM(G36:G41)</f>
+        <v/>
+      </c>
+      <c r="H35" s="10">
+        <f>SUM(H36:H41)</f>
+        <v/>
+      </c>
+      <c r="I35" s="10">
+        <f>SUM(I36:I41)</f>
+        <v/>
+      </c>
+      <c r="J35" s="10">
+        <f>SUM(J36:J41)</f>
+        <v/>
+      </c>
+      <c r="K35" s="10">
+        <f>SUM(K36:K41)</f>
+        <v/>
+      </c>
+      <c r="L35" s="10">
+        <f>SUM(L36:L41)</f>
+        <v/>
+      </c>
+      <c r="M35" s="10">
+        <f>SUM(M36:M41)</f>
+        <v/>
+      </c>
+      <c r="N35" s="10">
+        <f>SUM(N36:N41)</f>
+        <v/>
+      </c>
+      <c r="O35" s="10">
+        <f>SUM(O36:O41)</f>
+        <v/>
+      </c>
+      <c r="P35" s="10">
         <f>SUM(D35:O35)</f>
         <v/>
       </c>
-      <c r="Q35" s="4" t="inlineStr">
+      <c r="Q35" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -2561,7 +2531,7 @@
     <row r="36" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">      DELAWARE</t>
+          <t xml:space="preserve">      CONTINUUM</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -2618,12 +2588,16 @@
         <f>SUM(D36:O36)</f>
         <v/>
       </c>
-      <c r="Q36" s="4" t="n"/>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="37" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">      HUSHED</t>
+          <t xml:space="preserve">      DELAWARE</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -2685,7 +2659,7 @@
     <row r="38" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">      IPOSTAL</t>
+          <t xml:space="preserve">      HUSHED</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -2747,7 +2721,7 @@
     <row r="39" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">      QUICKBOOKS</t>
+          <t xml:space="preserve">      IPOSTAL</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -2809,7 +2783,7 @@
     <row r="40" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">      REGUS</t>
+          <t xml:space="preserve">      QUICKBOOKS</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -2868,199 +2842,195 @@
       </c>
       <c r="Q40" s="4" t="n"/>
     </row>
-    <row r="41" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="41" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      REGUS</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="E41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="F41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="G41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="H41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="I41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="J41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="K41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="L41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="M41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="N41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="O41" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A41))</f>
+        <v/>
+      </c>
+      <c r="P41" s="4">
+        <f>SUM(D41:O41)</f>
+        <v/>
+      </c>
+      <c r="Q41" s="4" t="n"/>
+    </row>
+    <row r="42" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Technology</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10">
-        <f>SUM(D42:D42)</f>
-        <v/>
-      </c>
-      <c r="E41" s="10">
-        <f>SUM(E42:E42)</f>
-        <v/>
-      </c>
-      <c r="F41" s="10">
-        <f>SUM(F42:F42)</f>
-        <v/>
-      </c>
-      <c r="G41" s="10">
-        <f>SUM(G42:G42)</f>
-        <v/>
-      </c>
-      <c r="H41" s="10">
-        <f>SUM(H42:H42)</f>
-        <v/>
-      </c>
-      <c r="I41" s="10">
-        <f>SUM(I42:I42)</f>
-        <v/>
-      </c>
-      <c r="J41" s="10">
-        <f>SUM(J42:J42)</f>
-        <v/>
-      </c>
-      <c r="K41" s="10">
-        <f>SUM(K42:K42)</f>
-        <v/>
-      </c>
-      <c r="L41" s="10">
-        <f>SUM(L42:L42)</f>
-        <v/>
-      </c>
-      <c r="M41" s="10">
-        <f>SUM(M42:M42)</f>
-        <v/>
-      </c>
-      <c r="N41" s="10">
-        <f>SUM(N42:N42)</f>
-        <v/>
-      </c>
-      <c r="O41" s="10">
-        <f>SUM(O42:O42)</f>
-        <v/>
-      </c>
-      <c r="P41" s="10">
-        <f>SUM(D41:O41)</f>
-        <v/>
-      </c>
-      <c r="Q41" s="10" t="inlineStr">
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10">
+        <f>SUM(D43:D43)</f>
+        <v/>
+      </c>
+      <c r="E42" s="10">
+        <f>SUM(E43:E43)</f>
+        <v/>
+      </c>
+      <c r="F42" s="10">
+        <f>SUM(F43:F43)</f>
+        <v/>
+      </c>
+      <c r="G42" s="10">
+        <f>SUM(G43:G43)</f>
+        <v/>
+      </c>
+      <c r="H42" s="10">
+        <f>SUM(H43:H43)</f>
+        <v/>
+      </c>
+      <c r="I42" s="10">
+        <f>SUM(I43:I43)</f>
+        <v/>
+      </c>
+      <c r="J42" s="10">
+        <f>SUM(J43:J43)</f>
+        <v/>
+      </c>
+      <c r="K42" s="10">
+        <f>SUM(K43:K43)</f>
+        <v/>
+      </c>
+      <c r="L42" s="10">
+        <f>SUM(L43:L43)</f>
+        <v/>
+      </c>
+      <c r="M42" s="10">
+        <f>SUM(M43:M43)</f>
+        <v/>
+      </c>
+      <c r="N42" s="10">
+        <f>SUM(N43:N43)</f>
+        <v/>
+      </c>
+      <c r="O42" s="10">
+        <f>SUM(O43:O43)</f>
+        <v/>
+      </c>
+      <c r="P42" s="10">
+        <f>SUM(D42:O42)</f>
+        <v/>
+      </c>
+      <c r="Q42" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="42" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t xml:space="preserve">      REVER</t>
         </is>
       </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="E42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="F42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="G42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="H42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="I42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="J42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="K42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="L42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="M42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="N42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="O42" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
-        <v/>
-      </c>
-      <c r="P42" s="4">
-        <f>SUM(D42:O42)</f>
-        <v/>
-      </c>
-      <c r="Q42" s="4" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Uncategorized Expenses</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="E43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="F43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="G43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="H43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="I43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="J43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="K43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="L43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="M43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="N43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="O43" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="P43" s="10">
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="E43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="F43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="G43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="H43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="I43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="J43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="K43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="L43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="M43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="N43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="O43" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
+        <v/>
+      </c>
+      <c r="P43" s="4">
         <f>SUM(D43:O43)</f>
         <v/>
       </c>
-      <c r="Q43" s="10" t="inlineStr">
+      <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -3069,212 +3039,247 @@
     <row r="44" hidden="1" outlineLevel="2" ht="12" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Currency Adjustment</t>
+          <t xml:space="preserve">    Uncategorized Expenses</t>
         </is>
       </c>
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
-      <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="n"/>
-      <c r="J44" s="10" t="n"/>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="10" t="n"/>
-      <c r="M44" s="10" t="n"/>
-      <c r="N44" s="10" t="n"/>
-      <c r="O44" s="10" t="n"/>
+      <c r="D44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="E44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="F44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="G44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="H44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="I44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="J44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="K44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="L44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="M44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="N44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="O44" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
       <c r="P44" s="10">
         <f>SUM(D44:O44)</f>
         <v/>
       </c>
-      <c r="Q44" s="10" t="n"/>
-    </row>
-    <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-      <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="4" t="n"/>
-      <c r="O45" s="4" t="n"/>
-      <c r="P45" s="4">
+      <c r="Q44" s="10" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="10" t="n"/>
+      <c r="K45" s="10" t="n"/>
+      <c r="L45" s="10" t="n"/>
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="10" t="n"/>
+      <c r="O45" s="10" t="n"/>
+      <c r="P45" s="10">
         <f>SUM(D45:O45)</f>
         <v/>
       </c>
-      <c r="Q45" s="4" t="n"/>
+      <c r="Q45" s="10" t="n"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4">
+        <f>SUM(D46:O46)</f>
+        <v/>
+      </c>
+      <c r="Q46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="12" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>PROFIT</t>
         </is>
       </c>
-      <c r="B46" s="13" t="n"/>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13">
-        <f>D4-D12-D31-D44</f>
-        <v/>
-      </c>
-      <c r="E46" s="13">
-        <f>E4-E12-E31-E44</f>
-        <v/>
-      </c>
-      <c r="F46" s="13">
-        <f>F4-F12-F31-F44</f>
-        <v/>
-      </c>
-      <c r="G46" s="13">
-        <f>G4-G12-G31-G44</f>
-        <v/>
-      </c>
-      <c r="H46" s="13">
-        <f>H4-H12-H31-H44</f>
-        <v/>
-      </c>
-      <c r="I46" s="13">
-        <f>I4-I12-I31-I44</f>
-        <v/>
-      </c>
-      <c r="J46" s="13">
-        <f>J4-J12-J31-J44</f>
-        <v/>
-      </c>
-      <c r="K46" s="13">
-        <f>K4-K12-K31-K44</f>
-        <v/>
-      </c>
-      <c r="L46" s="13">
-        <f>L4-L12-L31-L44</f>
-        <v/>
-      </c>
-      <c r="M46" s="13">
-        <f>M4-M12-M31-M44</f>
-        <v/>
-      </c>
-      <c r="N46" s="13">
-        <f>N4-N12-N31-N44</f>
-        <v/>
-      </c>
-      <c r="O46" s="13">
-        <f>O4-O12-O31-O44</f>
-        <v/>
-      </c>
-      <c r="P46" s="13">
-        <f>SUM(D46:O46)</f>
-        <v/>
-      </c>
-      <c r="Q46" s="13" t="n"/>
-    </row>
-    <row r="47" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="B47" s="14" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="14">
+        <f>D4-D12-D32-D45</f>
+        <v/>
+      </c>
+      <c r="E47" s="14">
+        <f>E4-E12-E32-E45</f>
+        <v/>
+      </c>
+      <c r="F47" s="14">
+        <f>F4-F12-F32-F45</f>
+        <v/>
+      </c>
+      <c r="G47" s="14">
+        <f>G4-G12-G32-G45</f>
+        <v/>
+      </c>
+      <c r="H47" s="14">
+        <f>H4-H12-H32-H45</f>
+        <v/>
+      </c>
+      <c r="I47" s="14">
+        <f>I4-I12-I32-I45</f>
+        <v/>
+      </c>
+      <c r="J47" s="14">
+        <f>J4-J12-J32-J45</f>
+        <v/>
+      </c>
+      <c r="K47" s="14">
+        <f>K4-K12-K32-K45</f>
+        <v/>
+      </c>
+      <c r="L47" s="14">
+        <f>L4-L12-L32-L45</f>
+        <v/>
+      </c>
+      <c r="M47" s="14">
+        <f>M4-M12-M32-M45</f>
+        <v/>
+      </c>
+      <c r="N47" s="14">
+        <f>N4-N12-N32-N45</f>
+        <v/>
+      </c>
+      <c r="O47" s="14">
+        <f>O4-O12-O32-O45</f>
+        <v/>
+      </c>
+      <c r="P47" s="14">
+        <f>SUM(D47:O47)</f>
+        <v/>
+      </c>
+      <c r="Q47" s="14" t="n"/>
+    </row>
+    <row r="48" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>% profit / product sales</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11">
-        <f>IFERROR(D46/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E47" s="11">
-        <f>IFERROR(E46/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F47" s="11">
-        <f>IFERROR(F46/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G47" s="11">
-        <f>IFERROR(G46/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H47" s="11">
-        <f>IFERROR(H46/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I47" s="11">
-        <f>IFERROR(I46/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J47" s="11">
-        <f>IFERROR(J46/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K47" s="11">
-        <f>IFERROR(K46/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L47" s="11">
-        <f>IFERROR(L46/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M47" s="11">
-        <f>IFERROR(M46/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N47" s="11">
-        <f>IFERROR(N46/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O47" s="11">
-        <f>IFERROR(O46/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P47" s="11">
-        <f>IFERROR(P46/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q47" s="11" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="n"/>
-      <c r="L48" s="4" t="n"/>
-      <c r="M48" s="4" t="n"/>
-      <c r="N48" s="4" t="n"/>
-      <c r="O48" s="4" t="n"/>
-      <c r="P48" s="4" t="n"/>
-      <c r="Q48" s="4" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11">
+        <f>IFERROR(D47/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E48" s="11">
+        <f>IFERROR(E47/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F48" s="11">
+        <f>IFERROR(F47/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IFERROR(G47/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H48" s="11">
+        <f>IFERROR(H47/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I48" s="11">
+        <f>IFERROR(I47/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J48" s="11">
+        <f>IFERROR(J47/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K48" s="11">
+        <f>IFERROR(K47/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L48" s="11">
+        <f>IFERROR(L47/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M48" s="11">
+        <f>IFERROR(M47/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N48" s="11">
+        <f>IFERROR(N47/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O48" s="11">
+        <f>IFERROR(O47/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P48" s="11">
+        <f>IFERROR(P47/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q48" s="11" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>Stock inicial marcos</t>
-        </is>
-      </c>
       <c r="B49" s="4" t="n"/>
       <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n">
-        <v>15764.34</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>13105.38</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>11635.01</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>10232.85</v>
-      </c>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
       <c r="H49" s="4" t="n"/>
       <c r="I49" s="4" t="n"/>
       <c r="J49" s="4" t="n"/>
@@ -3283,31 +3288,28 @@
       <c r="M49" s="4" t="n"/>
       <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
-      <c r="P49" s="4">
-        <f>SUM(D49:O49)</f>
-        <v/>
-      </c>
+      <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>Stock final marcos</t>
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>Stock inicial marcos</t>
         </is>
       </c>
       <c r="B50" s="4" t="n"/>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n">
+        <v>15764.34</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>13105.38</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="F50" s="4" t="n">
         <v>11635.01</v>
       </c>
-      <c r="F50" s="4" t="n">
-        <v>10217.07</v>
-      </c>
       <c r="G50" s="4" t="n">
-        <v>10174.5</v>
+        <v>10232.85</v>
       </c>
       <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="n"/>
@@ -3322,6 +3324,40 @@
         <v/>
       </c>
       <c r="Q50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>Stock final marcos</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n">
+        <v>13105.38</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>11635.01</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>10217.07</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>10165.55</v>
+      </c>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
+      <c r="P51" s="4">
+        <f>SUM(D51:O51)</f>
+        <v/>
+      </c>
+      <c r="Q51" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3337,13 +3373,13 @@
     <hyperlink ref="Q19" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q21" location="'g-payment-fees-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q22" location="'g-payment-fees-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q32" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q33" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q34" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q35" location="'g-expenses-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q41" location="'g-expenses-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q36" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q42" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q43" location="'g-expenses-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q44" location="'g-expenses-inc'!A1" display="-&gt;"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3363,19 +3399,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -3423,7 +3459,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-04T10:00:17Z</t>
+          <t>2026-04-10T09:48:04Z</t>
         </is>
       </c>
     </row>
@@ -3457,59 +3493,59 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>line_item</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="J2" s="17" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -3549,7 +3585,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H3" s="17" t="n">
+      <c r="H3" s="18" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
@@ -3595,7 +3631,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="18" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
@@ -3641,7 +3677,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="18" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
@@ -3675,7 +3711,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1645.88</v>
+        <v>4493.94</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3687,11 +3723,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1645.88</v>
+        <v>4493.94</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3713,7 +3749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3733,79 +3769,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>subcategory</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="J2" s="17" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="K2" s="16" t="inlineStr">
+      <c r="K2" s="17" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="L2" s="16" t="inlineStr">
+      <c r="L2" s="17" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="M2" s="16" t="inlineStr">
+      <c r="M2" s="17" t="inlineStr">
         <is>
           <t>invoice_number</t>
         </is>
       </c>
-      <c r="N2" s="16" t="inlineStr">
+      <c r="N2" s="17" t="inlineStr">
         <is>
           <t>drive_url</t>
         </is>
@@ -3855,7 +3891,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J3" s="17" t="n">
+      <c r="J3" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
@@ -3866,7 +3902,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M3" s="18" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>1220</t>
         </is>
@@ -3921,7 +3957,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
@@ -3932,7 +3968,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M4" s="18" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t>2172-2199</t>
         </is>
@@ -3987,7 +4023,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="J5" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
@@ -3998,7 +4034,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M5" s="18" t="inlineStr">
+      <c r="M5" s="19" t="inlineStr">
         <is>
           <t>34735793</t>
         </is>
@@ -4053,7 +4089,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
@@ -4064,7 +4100,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M6" s="18" t="inlineStr">
+      <c r="M6" s="19" t="inlineStr">
         <is>
           <t>34899776</t>
         </is>
@@ -4119,7 +4155,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
@@ -4130,7 +4166,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M7" s="18" t="inlineStr">
+      <c r="M7" s="19" t="inlineStr">
         <is>
           <t>35170891</t>
         </is>
@@ -4185,7 +4221,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
@@ -4196,7 +4232,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M8" s="18" t="inlineStr">
+      <c r="M8" s="19" t="inlineStr">
         <is>
           <t>35204899</t>
         </is>
@@ -4251,7 +4287,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
@@ -4262,7 +4298,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M9" s="18" t="inlineStr">
+      <c r="M9" s="19" t="inlineStr">
         <is>
           <t>AS-93451</t>
         </is>
@@ -4317,7 +4353,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
@@ -4328,7 +4364,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M10" s="18" t="inlineStr">
+      <c r="M10" s="19" t="inlineStr">
         <is>
           <t>AS-94908</t>
         </is>
@@ -4383,7 +4419,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
@@ -4394,7 +4430,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M11" s="18" t="inlineStr">
+      <c r="M11" s="19" t="inlineStr">
         <is>
           <t>AS-94969</t>
         </is>
@@ -4449,7 +4485,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J12" s="17" t="n">
+      <c r="J12" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
@@ -4460,7 +4496,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M12" s="18" t="inlineStr">
+      <c r="M12" s="19" t="inlineStr">
         <is>
           <t>AS-95058</t>
         </is>
@@ -4515,7 +4551,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
@@ -4526,7 +4562,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M13" s="18" t="inlineStr">
+      <c r="M13" s="19" t="inlineStr">
         <is>
           <t>AS-95513</t>
         </is>
@@ -4581,7 +4617,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
@@ -4592,7 +4628,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M14" s="18" t="inlineStr">
+      <c r="M14" s="19" t="inlineStr">
         <is>
           <t>AS-96265</t>
         </is>
@@ -4647,7 +4683,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J15" s="17" t="n">
+      <c r="J15" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
@@ -4658,7 +4694,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M15" s="18" t="inlineStr">
+      <c r="M15" s="19" t="inlineStr">
         <is>
           <t>AS-96361</t>
         </is>
@@ -4713,7 +4749,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J16" s="17" t="n">
+      <c r="J16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
@@ -4724,7 +4760,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M16" s="18" t="inlineStr">
+      <c r="M16" s="19" t="inlineStr">
         <is>
           <t>10001458238017</t>
         </is>
@@ -4779,7 +4815,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
@@ -4790,7 +4826,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M17" s="18" t="inlineStr">
+      <c r="M17" s="19" t="inlineStr">
         <is>
           <t>3313-43306</t>
         </is>
@@ -4845,7 +4881,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="18" t="n">
         <v>1.1919</v>
       </c>
       <c r="K18" s="4" t="n">
@@ -4856,7 +4892,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M18" s="18" t="inlineStr">
+      <c r="M18" s="19" t="inlineStr">
         <is>
           <t>2026-0009</t>
         </is>
@@ -4911,7 +4947,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="J19" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="4" t="n">
@@ -4922,7 +4958,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M19" s="18" t="inlineStr">
+      <c r="M19" s="19" t="inlineStr">
         <is>
           <t>171197</t>
         </is>
@@ -4977,7 +5013,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
@@ -4988,7 +5024,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M20" s="18" t="inlineStr">
+      <c r="M20" s="19" t="inlineStr">
         <is>
           <t>171198</t>
         </is>
@@ -5043,7 +5079,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J21" s="17" t="n">
+      <c r="J21" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="4" t="n">
@@ -5054,7 +5090,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M21" s="18" t="inlineStr">
+      <c r="M21" s="19" t="inlineStr">
         <is>
           <t>1236</t>
         </is>
@@ -5109,7 +5145,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J22" s="17" t="n">
+      <c r="J22" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="4" t="n">
@@ -5120,7 +5156,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M22" s="18" t="inlineStr">
+      <c r="M22" s="19" t="inlineStr">
         <is>
           <t>2353-3823</t>
         </is>
@@ -5175,7 +5211,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J23" s="17" t="n">
+      <c r="J23" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="4" t="n">
@@ -5186,7 +5222,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M23" s="18" t="inlineStr">
+      <c r="M23" s="19" t="inlineStr">
         <is>
           <t>35389577</t>
         </is>
@@ -5241,7 +5277,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J24" s="17" t="n">
+      <c r="J24" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="4" t="n">
@@ -5252,7 +5288,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M24" s="18" t="inlineStr">
+      <c r="M24" s="19" t="inlineStr">
         <is>
           <t>35565709</t>
         </is>
@@ -5307,7 +5343,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J25" s="17" t="n">
+      <c r="J25" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="4" t="n">
@@ -5318,7 +5354,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M25" s="18" t="inlineStr">
+      <c r="M25" s="19" t="inlineStr">
         <is>
           <t>35722393</t>
         </is>
@@ -5373,7 +5409,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J26" s="17" t="n">
+      <c r="J26" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="4" t="n">
@@ -5384,7 +5420,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M26" s="18" t="inlineStr">
+      <c r="M26" s="19" t="inlineStr">
         <is>
           <t>35894810</t>
         </is>
@@ -5439,7 +5475,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J27" s="17" t="n">
+      <c r="J27" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="4" t="n">
@@ -5450,7 +5486,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M27" s="18" t="inlineStr">
+      <c r="M27" s="19" t="inlineStr">
         <is>
           <t>35920058</t>
         </is>
@@ -5505,7 +5541,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J28" s="17" t="n">
+      <c r="J28" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
@@ -5516,7 +5552,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M28" s="18" t="inlineStr">
+      <c r="M28" s="19" t="inlineStr">
         <is>
           <t>AS-97102</t>
         </is>
@@ -5571,7 +5607,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J29" s="17" t="n">
+      <c r="J29" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="n">
@@ -5582,7 +5618,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M29" s="18" t="inlineStr">
+      <c r="M29" s="19" t="inlineStr">
         <is>
           <t>AS-97313</t>
         </is>
@@ -5637,7 +5673,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J30" s="17" t="n">
+      <c r="J30" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="4" t="n">
@@ -5648,7 +5684,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M30" s="18" t="inlineStr">
+      <c r="M30" s="19" t="inlineStr">
         <is>
           <t>AS-97766</t>
         </is>
@@ -5703,7 +5739,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J31" s="17" t="n">
+      <c r="J31" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="n">
@@ -5714,7 +5750,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M31" s="18" t="inlineStr">
+      <c r="M31" s="19" t="inlineStr">
         <is>
           <t>AS-97929</t>
         </is>
@@ -5769,7 +5805,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J32" s="17" t="n">
+      <c r="J32" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="4" t="n">
@@ -5780,7 +5816,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M32" s="18" t="inlineStr">
+      <c r="M32" s="19" t="inlineStr">
         <is>
           <t>AS-98182</t>
         </is>
@@ -5835,7 +5871,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J33" s="17" t="n">
+      <c r="J33" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="4" t="n">
@@ -5846,7 +5882,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M33" s="18" t="inlineStr">
+      <c r="M33" s="19" t="inlineStr">
         <is>
           <t>AS-98184</t>
         </is>
@@ -5901,7 +5937,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J34" s="17" t="n">
+      <c r="J34" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="4" t="n">
@@ -5912,7 +5948,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M34" s="18" t="inlineStr">
+      <c r="M34" s="19" t="inlineStr">
         <is>
           <t>AS-98186</t>
         </is>
@@ -5967,7 +6003,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J35" s="17" t="n">
+      <c r="J35" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="4" t="n">
@@ -5978,7 +6014,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M35" s="18" t="inlineStr">
+      <c r="M35" s="19" t="inlineStr">
         <is>
           <t>AS-98295</t>
         </is>
@@ -6033,7 +6069,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J36" s="17" t="n">
+      <c r="J36" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="4" t="n">
@@ -6044,7 +6080,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M36" s="18" t="inlineStr">
+      <c r="M36" s="19" t="inlineStr">
         <is>
           <t>AS-98569</t>
         </is>
@@ -6099,7 +6135,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J37" s="17" t="n">
+      <c r="J37" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="4" t="n">
@@ -6110,7 +6146,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M37" s="18" t="inlineStr">
+      <c r="M37" s="19" t="inlineStr">
         <is>
           <t>AS-98850</t>
         </is>
@@ -6165,7 +6201,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J38" s="17" t="n">
+      <c r="J38" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="4" t="n">
@@ -6176,7 +6212,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M38" s="18" t="inlineStr">
+      <c r="M38" s="19" t="inlineStr">
         <is>
           <t>AS-99137</t>
         </is>
@@ -6231,7 +6267,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J39" s="17" t="n">
+      <c r="J39" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="4" t="n">
@@ -6242,7 +6278,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M39" s="18" t="inlineStr">
+      <c r="M39" s="19" t="inlineStr">
         <is>
           <t>AS-99148</t>
         </is>
@@ -6297,7 +6333,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J40" s="17" t="n">
+      <c r="J40" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="4" t="n">
@@ -6308,7 +6344,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M40" s="18" t="inlineStr">
+      <c r="M40" s="19" t="inlineStr">
         <is>
           <t>AS-99337</t>
         </is>
@@ -6363,7 +6399,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J41" s="17" t="n">
+      <c r="J41" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="4" t="n">
@@ -6374,7 +6410,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M41" s="18" t="inlineStr">
+      <c r="M41" s="19" t="inlineStr">
         <is>
           <t>AS-99436</t>
         </is>
@@ -6429,7 +6465,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J42" s="17" t="n">
+      <c r="J42" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="4" t="n">
@@ -6440,7 +6476,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M42" s="18" t="inlineStr">
+      <c r="M42" s="19" t="inlineStr">
         <is>
           <t>AS-99460</t>
         </is>
@@ -6495,7 +6531,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J43" s="17" t="n">
+      <c r="J43" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="4" t="n">
@@ -6506,7 +6542,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M43" s="18" t="inlineStr">
+      <c r="M43" s="19" t="inlineStr">
         <is>
           <t>AS-99461</t>
         </is>
@@ -6561,7 +6597,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J44" s="17" t="n">
+      <c r="J44" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="4" t="n">
@@ -6572,7 +6608,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M44" s="18" t="inlineStr">
+      <c r="M44" s="19" t="inlineStr">
         <is>
           <t>AS-99636</t>
         </is>
@@ -6627,7 +6663,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J45" s="17" t="n">
+      <c r="J45" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K45" s="4" t="n">
@@ -6638,7 +6674,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M45" s="18" t="inlineStr">
+      <c r="M45" s="19" t="inlineStr">
         <is>
           <t>AS-99795</t>
         </is>
@@ -6693,7 +6729,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J46" s="17" t="n">
+      <c r="J46" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K46" s="4" t="n">
@@ -6704,7 +6740,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M46" s="18" t="inlineStr">
+      <c r="M46" s="19" t="inlineStr">
         <is>
           <t>10001466838914</t>
         </is>
@@ -6759,7 +6795,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J47" s="17" t="n">
+      <c r="J47" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K47" s="4" t="n">
@@ -6770,7 +6806,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M47" s="18" t="inlineStr">
+      <c r="M47" s="19" t="inlineStr">
         <is>
           <t>3313-43718</t>
         </is>
@@ -6825,7 +6861,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J48" s="17" t="n">
+      <c r="J48" s="18" t="n">
         <v>1.1805</v>
       </c>
       <c r="K48" s="4" t="n">
@@ -6836,7 +6872,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M48" s="18" t="inlineStr">
+      <c r="M48" s="19" t="inlineStr">
         <is>
           <t>2026-0014</t>
         </is>
@@ -6891,7 +6927,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J49" s="17" t="n">
+      <c r="J49" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K49" s="4" t="n">
@@ -6902,7 +6938,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M49" s="18" t="inlineStr">
+      <c r="M49" s="19" t="inlineStr">
         <is>
           <t>171420</t>
         </is>
@@ -6957,7 +6993,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J50" s="17" t="n">
+      <c r="J50" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K50" s="4" t="n">
@@ -6968,7 +7004,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M50" s="18" t="inlineStr">
+      <c r="M50" s="19" t="inlineStr">
         <is>
           <t>171421</t>
         </is>
@@ -7023,7 +7059,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J51" s="17" t="n">
+      <c r="J51" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="4" t="n">
@@ -7034,7 +7070,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M51" s="18" t="inlineStr">
+      <c r="M51" s="19" t="inlineStr">
         <is>
           <t>1253</t>
         </is>
@@ -7089,7 +7125,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J52" s="17" t="n">
+      <c r="J52" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K52" s="4" t="n">
@@ -7100,7 +7136,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M52" s="18" t="inlineStr">
+      <c r="M52" s="19" t="inlineStr">
         <is>
           <t>6FF58AC</t>
         </is>
@@ -7155,7 +7191,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J53" s="17" t="n">
+      <c r="J53" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="4" t="n">
@@ -7166,7 +7202,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M53" s="18" t="inlineStr">
+      <c r="M53" s="19" t="inlineStr">
         <is>
           <t>2262-7837</t>
         </is>
@@ -7221,7 +7257,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J54" s="17" t="n">
+      <c r="J54" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="4" t="n">
@@ -7232,7 +7268,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M54" s="18" t="inlineStr">
+      <c r="M54" s="19" t="inlineStr">
         <is>
           <t>36093781</t>
         </is>
@@ -7287,7 +7323,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J55" s="17" t="n">
+      <c r="J55" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K55" s="4" t="n">
@@ -7298,7 +7334,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M55" s="18" t="inlineStr">
+      <c r="M55" s="19" t="inlineStr">
         <is>
           <t>36265975</t>
         </is>
@@ -7353,7 +7389,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J56" s="17" t="n">
+      <c r="J56" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="4" t="n">
@@ -7364,7 +7400,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M56" s="18" t="inlineStr">
+      <c r="M56" s="19" t="inlineStr">
         <is>
           <t>36427002</t>
         </is>
@@ -7419,7 +7455,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J57" s="17" t="n">
+      <c r="J57" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="4" t="n">
@@ -7430,7 +7466,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M57" s="18" t="inlineStr">
+      <c r="M57" s="19" t="inlineStr">
         <is>
           <t>36541238</t>
         </is>
@@ -7485,7 +7521,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J58" s="17" t="n">
+      <c r="J58" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="4" t="n">
@@ -7496,7 +7532,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M58" s="18" t="inlineStr">
+      <c r="M58" s="19" t="inlineStr">
         <is>
           <t>36584953</t>
         </is>
@@ -7551,7 +7587,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J59" s="17" t="n">
+      <c r="J59" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K59" s="4" t="n">
@@ -7562,7 +7598,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M59" s="18" t="inlineStr">
+      <c r="M59" s="19" t="inlineStr">
         <is>
           <t>36600953</t>
         </is>
@@ -7617,7 +7653,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J60" s="17" t="n">
+      <c r="J60" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K60" s="4" t="n">
@@ -7628,7 +7664,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M60" s="18" t="inlineStr">
+      <c r="M60" s="19" t="inlineStr">
         <is>
           <t>AS-100001</t>
         </is>
@@ -7683,7 +7719,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J61" s="17" t="n">
+      <c r="J61" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K61" s="4" t="n">
@@ -7694,7 +7730,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M61" s="18" t="inlineStr">
+      <c r="M61" s="19" t="inlineStr">
         <is>
           <t>AS-100189</t>
         </is>
@@ -7749,7 +7785,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J62" s="17" t="n">
+      <c r="J62" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="4" t="n">
@@ -7760,7 +7796,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M62" s="18" t="inlineStr">
+      <c r="M62" s="19" t="inlineStr">
         <is>
           <t>AS-100208</t>
         </is>
@@ -7815,7 +7851,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J63" s="17" t="n">
+      <c r="J63" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="4" t="n">
@@ -7826,7 +7862,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M63" s="18" t="inlineStr">
+      <c r="M63" s="19" t="inlineStr">
         <is>
           <t>AS-100505</t>
         </is>
@@ -7881,7 +7917,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J64" s="17" t="n">
+      <c r="J64" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="4" t="n">
@@ -7892,7 +7928,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M64" s="18" t="inlineStr">
+      <c r="M64" s="19" t="inlineStr">
         <is>
           <t>AS-100874</t>
         </is>
@@ -7947,7 +7983,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J65" s="17" t="n">
+      <c r="J65" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="4" t="n">
@@ -7958,7 +7994,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M65" s="18" t="inlineStr">
+      <c r="M65" s="19" t="inlineStr">
         <is>
           <t>AS-100996</t>
         </is>
@@ -8013,7 +8049,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J66" s="17" t="n">
+      <c r="J66" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K66" s="4" t="n">
@@ -8024,7 +8060,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M66" s="18" t="inlineStr">
+      <c r="M66" s="19" t="inlineStr">
         <is>
           <t>AS-101113</t>
         </is>
@@ -8079,7 +8115,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J67" s="17" t="n">
+      <c r="J67" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K67" s="4" t="n">
@@ -8090,7 +8126,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M67" s="18" t="inlineStr">
+      <c r="M67" s="19" t="inlineStr">
         <is>
           <t>AS-101200</t>
         </is>
@@ -8145,7 +8181,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J68" s="17" t="n">
+      <c r="J68" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K68" s="4" t="n">
@@ -8156,7 +8192,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M68" s="18" t="inlineStr">
+      <c r="M68" s="19" t="inlineStr">
         <is>
           <t>AS-101203</t>
         </is>
@@ -8211,7 +8247,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J69" s="17" t="n">
+      <c r="J69" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="4" t="n">
@@ -8222,7 +8258,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M69" s="18" t="inlineStr">
+      <c r="M69" s="19" t="inlineStr">
         <is>
           <t>AS-101378</t>
         </is>
@@ -8277,7 +8313,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J70" s="17" t="n">
+      <c r="J70" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="4" t="n">
@@ -8288,7 +8324,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M70" s="18" t="inlineStr">
+      <c r="M70" s="19" t="inlineStr">
         <is>
           <t>AS-101565</t>
         </is>
@@ -8343,7 +8379,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J71" s="17" t="n">
+      <c r="J71" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K71" s="4" t="n">
@@ -8354,7 +8390,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M71" s="18" t="inlineStr">
+      <c r="M71" s="19" t="inlineStr">
         <is>
           <t>AS-101625</t>
         </is>
@@ -8409,7 +8445,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J72" s="17" t="n">
+      <c r="J72" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K72" s="4" t="n">
@@ -8420,7 +8456,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M72" s="18" t="inlineStr">
+      <c r="M72" s="19" t="inlineStr">
         <is>
           <t>AS-101687</t>
         </is>
@@ -8475,7 +8511,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J73" s="17" t="n">
+      <c r="J73" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K73" s="4" t="n">
@@ -8486,7 +8522,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M73" s="18" t="inlineStr">
+      <c r="M73" s="19" t="inlineStr">
         <is>
           <t>AS-101720</t>
         </is>
@@ -8541,7 +8577,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J74" s="17" t="n">
+      <c r="J74" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K74" s="4" t="n">
@@ -8552,7 +8588,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M74" s="18" t="inlineStr">
+      <c r="M74" s="19" t="inlineStr">
         <is>
           <t>AS-101875</t>
         </is>
@@ -8607,7 +8643,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J75" s="17" t="n">
+      <c r="J75" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K75" s="4" t="n">
@@ -8618,7 +8654,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M75" s="18" t="inlineStr">
+      <c r="M75" s="19" t="inlineStr">
         <is>
           <t>AS-101899</t>
         </is>
@@ -8673,7 +8709,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J76" s="17" t="n">
+      <c r="J76" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K76" s="4" t="n">
@@ -8684,7 +8720,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M76" s="18" t="inlineStr">
+      <c r="M76" s="19" t="inlineStr">
         <is>
           <t>AS-101925</t>
         </is>
@@ -8739,7 +8775,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J77" s="17" t="n">
+      <c r="J77" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K77" s="4" t="n">
@@ -8750,7 +8786,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M77" s="18" t="inlineStr">
+      <c r="M77" s="19" t="inlineStr">
         <is>
           <t>AS-101927</t>
         </is>
@@ -8805,7 +8841,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J78" s="17" t="n">
+      <c r="J78" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K78" s="4" t="n">
@@ -8816,7 +8852,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M78" s="18" t="inlineStr">
+      <c r="M78" s="19" t="inlineStr">
         <is>
           <t>AS-101932</t>
         </is>
@@ -8871,7 +8907,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J79" s="17" t="n">
+      <c r="J79" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K79" s="4" t="n">
@@ -8882,7 +8918,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M79" s="18" t="inlineStr">
+      <c r="M79" s="19" t="inlineStr">
         <is>
           <t>AS-102156</t>
         </is>
@@ -8937,7 +8973,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J80" s="17" t="n">
+      <c r="J80" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K80" s="4" t="n">
@@ -8948,7 +8984,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M80" s="18" t="inlineStr">
+      <c r="M80" s="19" t="inlineStr">
         <is>
           <t>AS-102233</t>
         </is>
@@ -9003,7 +9039,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J81" s="17" t="n">
+      <c r="J81" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
@@ -9014,7 +9050,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M81" s="18" t="inlineStr">
+      <c r="M81" s="19" t="inlineStr">
         <is>
           <t>AS-99872</t>
         </is>
@@ -9069,7 +9105,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J82" s="17" t="n">
+      <c r="J82" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K82" s="4" t="n">
@@ -9080,7 +9116,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M82" s="18" t="inlineStr">
+      <c r="M82" s="19" t="inlineStr">
         <is>
           <t>10001475281494</t>
         </is>
@@ -9094,66 +9130,198 @@
     <row r="83" ht="12" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>INC</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>shared_services</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>SHAREDSERVICESSL</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>7586.05</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J83" s="18" t="n">
+        <v>1.1498</v>
+      </c>
+      <c r="K83" s="4" t="n">
+        <v>8722.440000000001</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M83" s="19" t="inlineStr">
+        <is>
+          <t>2026-0017</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ixVdpnGpB3KUF2QQIt94W1I4J6yD6ybZ/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="12" customHeight="1">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>202604</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>opex</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>administration</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>CONTINUUM</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>invoice</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G84" s="4" t="n">
         <v>1150</v>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J83" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" s="4" t="n">
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J84" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="4" t="n">
         <v>1150</v>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M83" s="18" t="inlineStr">
+      <c r="M84" s="19" t="inlineStr">
         <is>
           <t>1268</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1IRL2tRQ5R66B1XtT5WF43fvSBNABo2MK/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="12" customHeight="1">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>INC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>DELAWARE</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J85" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M85" s="19" t="inlineStr">
+        <is>
+          <t>DZWHFH4</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/18Bz5GqwljLihnHs4k9hmETmifyo6LER2/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9241,6 +9409,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9267,54 +9437,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -9349,7 +9519,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G3" s="17" t="n">
+      <c r="G3" s="18" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="4" t="n">
@@ -9390,7 +9560,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="18" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
@@ -9431,7 +9601,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="18" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
@@ -9460,7 +9630,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>43.42</v>
+        <v>101</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -9472,11 +9642,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>43.42</v>
+        <v>101</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -9498,7 +9668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9511,44 +9681,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>rate_date</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>reference_rate</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -9575,10 +9745,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E3" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="17" t="n">
+      <c r="E3" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="18" t="n">
         <v>1.1919</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -9608,10 +9778,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="17" t="n">
+      <c r="E4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -9641,10 +9811,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="17" t="n">
+      <c r="E5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="18" t="n">
         <v>1.1805</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -9674,10 +9844,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="17" t="n">
+      <c r="E6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -9699,7 +9869,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -9707,46 +9877,79 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>1</v>
+      <c r="E7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>1.1498</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>identity</t>
+          <t>identity -&gt; https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
         </is>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="12" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>202604</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>identity</t>
         </is>
@@ -9777,34 +9980,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>current_folder</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>destination_path</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -9891,12 +10094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Delaware Corporate Headquarters LLC</t>
+          <t>DELAWARE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -9904,7 +10107,11 @@
           <t>expenses/opex/administration</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>US filing and registered office services</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="12" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -10139,7 +10346,7 @@
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Nº Facturas INC 2026</t>
         </is>
@@ -10213,151 +10420,151 @@
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Turnover</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="21" t="n">
+      <c r="B4" s="22" t="n"/>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" s="21" t="n"/>
+      <c r="Q4" s="22" t="n"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="A5" s="23" t="n"/>
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Product sales</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="22" t="n">
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="Q5" s="22" t="n"/>
+      <c r="Q5" s="23" t="n"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="A6" s="24" t="n"/>
-      <c r="B6" s="24" t="n"/>
+      <c r="A6" s="25" t="n"/>
+      <c r="B6" s="25" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="D6" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="24" t="n">
+      <c r="D6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" s="24" t="n"/>
+      <c r="Q6" s="25" t="n"/>
     </row>
     <row r="7" ht="12" customHeight="1">
       <c r="C7" t="inlineStr">
@@ -10406,250 +10613,250 @@
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="A8" s="23" t="n"/>
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="22" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="23" t="n"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="A9" s="24" t="n"/>
+      <c r="A9" s="25" t="n"/>
       <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Uncategorized income</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n"/>
-      <c r="D9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="24" t="n"/>
+      <c r="C9" s="25" t="n"/>
+      <c r="D9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="25" t="n"/>
     </row>
     <row r="10" ht="12" customHeight="1"/>
     <row r="11" ht="12" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n">
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="22" t="n">
         <v>31</v>
       </c>
-      <c r="F11" s="21" t="n">
-        <v>33</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="21" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q11" s="21" t="n"/>
+      <c r="F11" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="22" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q11" s="22" t="n"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="A12" s="23" t="n"/>
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n">
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="G12" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="22" t="n">
+      <c r="G12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="23" t="n">
         <v>55</v>
       </c>
-      <c r="Q12" s="22" t="n"/>
+      <c r="Q12" s="23" t="n"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="A13" s="24" t="n"/>
-      <c r="B13" s="24" t="n"/>
+      <c r="A13" s="25" t="n"/>
+      <c r="B13" s="25" t="n"/>
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="G13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="24" t="n">
+      <c r="G13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="25" t="n">
         <v>49</v>
       </c>
-      <c r="Q13" s="24" t="n"/>
+      <c r="Q13" s="25" t="n"/>
     </row>
     <row r="14" ht="12" customHeight="1">
       <c r="C14" t="inlineStr">
@@ -10666,7 +10873,7 @@
       <c r="F14" t="n">
         <v>22</v>
       </c>
-      <c r="G14" s="25" t="n">
+      <c r="G14" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
@@ -10744,53 +10951,53 @@
       </c>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="A16" s="24" t="n"/>
-      <c r="B16" s="24" t="n"/>
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="25" t="n"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Logistics</t>
         </is>
       </c>
-      <c r="D16" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="24" t="n">
+      <c r="D16" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="24" t="n"/>
+      <c r="Q16" s="25" t="n"/>
     </row>
     <row r="17" ht="12" customHeight="1">
       <c r="C17" t="inlineStr">
@@ -10839,53 +11046,53 @@
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="A18" s="24" t="n"/>
-      <c r="B18" s="24" t="n"/>
+      <c r="A18" s="25" t="n"/>
+      <c r="B18" s="25" t="n"/>
       <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Payment fees</t>
         </is>
       </c>
-      <c r="D18" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="24" t="n">
+      <c r="D18" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="Q18" s="24" t="n"/>
+      <c r="Q18" s="25" t="n"/>
     </row>
     <row r="19" ht="12" customHeight="1">
       <c r="C19" t="inlineStr">
@@ -10935,102 +11142,102 @@
     </row>
     <row r="20" ht="12" customHeight="1"/>
     <row r="21" ht="12" customHeight="1">
-      <c r="A21" s="22" t="n"/>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="A21" s="23" t="n"/>
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Opex</t>
         </is>
       </c>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n">
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="E21" s="22" t="n">
+      <c r="E21" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="F21" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q21" s="22" t="n"/>
+      <c r="F21" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="G21" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q21" s="23" t="n"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="A22" s="24" t="n"/>
-      <c r="B22" s="24" t="n"/>
+      <c r="A22" s="25" t="n"/>
+      <c r="B22" s="25" t="n"/>
       <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Shared services</t>
         </is>
       </c>
-      <c r="D22" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q22" s="24" t="n"/>
+      <c r="D22" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="25" t="n"/>
     </row>
     <row r="23" ht="12" customHeight="1">
       <c r="C23" t="inlineStr">
@@ -11045,9 +11252,9 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
@@ -11075,57 +11282,57 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" ht="12" customHeight="1">
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="25" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" ht="12" customHeight="1">
-      <c r="A24" s="24" t="n"/>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" s="24" t="n">
-        <v>9</v>
-      </c>
-      <c r="F24" s="24" t="n">
-        <v>10</v>
-      </c>
-      <c r="G24" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="24" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q24" s="24" t="n"/>
+      <c r="H24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="25" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q24" s="25" t="n"/>
     </row>
     <row r="25" ht="12" customHeight="1">
       <c r="C25" t="inlineStr">
@@ -11188,8 +11395,8 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="25" t="n">
-        <v>0</v>
+      <c r="G26" t="n">
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -11216,7 +11423,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" ht="12" customHeight="1">
@@ -11234,7 +11441,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
@@ -11280,7 +11487,7 @@
       <c r="F28" t="n">
         <v>6</v>
       </c>
-      <c r="G28" s="25" t="n">
+      <c r="G28" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
@@ -11326,7 +11533,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="25" t="n">
+      <c r="G29" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
@@ -11404,53 +11611,53 @@
       </c>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="A31" s="24" t="n"/>
-      <c r="B31" s="24" t="n"/>
+      <c r="A31" s="25" t="n"/>
+      <c r="B31" s="25" t="n"/>
       <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="24" t="n"/>
+      <c r="D31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="25" t="n"/>
     </row>
     <row r="32" ht="12" customHeight="1">
       <c r="C32" t="inlineStr">
@@ -11499,102 +11706,102 @@
       </c>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="A33" s="24" t="n"/>
-      <c r="B33" s="24" t="n"/>
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="25" t="n"/>
       <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Uncategorized Expenses</t>
         </is>
       </c>
-      <c r="D33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="24" t="n"/>
+      <c r="D33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="25" t="n"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="A34" s="24" t="n"/>
+      <c r="A34" s="25" t="n"/>
       <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Currency Adjustment</t>
         </is>
       </c>
-      <c r="C34" s="24" t="n"/>
-      <c r="D34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="24" t="n"/>
+      <c r="C34" s="25" t="n"/>
+      <c r="D34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/output/spreadsheet/pyg_inc_2026.xlsx
+++ b/output/spreadsheet/pyg_inc_2026.xlsx
@@ -702,7 +702,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Actualizado: 10/04/2026 11:48 h</t>
+          <t>Actualizado: 10/04/2026 12:53 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-10T09:48:04Z</t>
+          <t>2026-04-10T10:53:51Z</t>
         </is>
       </c>
     </row>
